--- a/inst/extdata/northern_cheyenne_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/northern_cheyenne_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/k_salkgundersen_tetratech_com/Documents/EPA/R8_AssessmentTool/5_Work/Crosswalks/individual_criteria_crosswalks/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A139C1B-8BB0-4A88-8D35-16F93C94BA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA0A469-B5C2-4040-8D3D-DDB2F3D596CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E55A9BC7-10AB-4EF2-8E95-202746609CFA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E55A9BC7-10AB-4EF2-8E95-202746609CFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="154">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -239,9 +239,6 @@
     <t>Hardness</t>
   </si>
   <si>
-    <t>Chromium III</t>
-  </si>
-  <si>
     <t>CHROMIUM(III)</t>
   </si>
   <si>
@@ -251,9 +248,6 @@
     <t>e^(0.819*[ln(hardness)]+0.6848)*0.860</t>
   </si>
   <si>
-    <t>Chromium VI</t>
-  </si>
-  <si>
     <t>CHROMIUM(VI)</t>
   </si>
   <si>
@@ -281,9 +275,6 @@
     <t>MERCURY</t>
   </si>
   <si>
-    <t>Mercury Methylmercury</t>
-  </si>
-  <si>
     <t>DIMETHYLMERCURY</t>
   </si>
   <si>
@@ -410,15 +401,9 @@
     <t>MANGANESE</t>
   </si>
   <si>
-    <t>Nitrates</t>
-  </si>
-  <si>
     <t>NITRATE</t>
   </si>
   <si>
-    <t>Dissolved Solids</t>
-  </si>
-  <si>
     <t>TOTAL DISSOLVED SOLIDS</t>
   </si>
   <si>
@@ -428,9 +413,6 @@
     <t>HYDROGEN SULFIDE</t>
   </si>
   <si>
-    <t>Oxygen</t>
-  </si>
-  <si>
     <t>DISSOLVED OXYGEN (DO)</t>
   </si>
   <si>
@@ -501,6 +483,21 @@
   </si>
   <si>
     <t>((0.0577/(1+10^(7.688-pH))) + (2.487/(1+10^(pH-7.688)))) * 1.45*10^(0.028*(25-Temperature))</t>
+  </si>
+  <si>
+    <t>CHROMIUM, TRIVALENT, TOTAL</t>
+  </si>
+  <si>
+    <t>CHROMIUM, HEXAVALENT</t>
+  </si>
+  <si>
+    <t>METHYLMERCURY</t>
+  </si>
+  <si>
+    <t>TOTAL DISSOLVED SOLIDS (TDS)</t>
+  </si>
+  <si>
+    <t>DISSOLVED OXYGEN</t>
   </si>
 </sst>
 </file>
@@ -910,9 +907,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88090834-75EE-4F17-A178-5F0CE015882D}">
   <dimension ref="A1:AQ69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="3" max="3" width="24.7265625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:43" s="4" customFormat="1" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:43" s="4" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1043,7 +1043,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
       <c r="B2" s="5" t="s">
         <v>43</v>
@@ -1110,7 +1110,7 @@
       <c r="AL2" s="5"/>
       <c r="AM2" s="5"/>
     </row>
-    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="5"/>
       <c r="B3" s="5" t="s">
         <v>43</v>
@@ -1177,7 +1177,7 @@
       <c r="AL3" s="5"/>
       <c r="AM3" s="5"/>
     </row>
-    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="5"/>
       <c r="B4" s="5" t="s">
         <v>43</v>
@@ -1248,7 +1248,7 @@
       <c r="AL4" s="5"/>
       <c r="AM4" s="5"/>
     </row>
-    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="5"/>
       <c r="B5" s="5" t="s">
         <v>43</v>
@@ -1319,7 +1319,7 @@
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
     </row>
-    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A6" s="5"/>
       <c r="B6" s="5" t="s">
         <v>43</v>
@@ -1388,7 +1388,7 @@
       <c r="AL6" s="5"/>
       <c r="AM6" s="5"/>
     </row>
-    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A7" s="5"/>
       <c r="B7" s="5" t="s">
         <v>43</v>
@@ -1457,7 +1457,7 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
     </row>
-    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A8" s="5"/>
       <c r="B8" s="5" t="s">
         <v>43</v>
@@ -1542,19 +1542,19 @@
       </c>
       <c r="AM8" s="5"/>
     </row>
-    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
       <c r="B9" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>63</v>
@@ -1602,13 +1602,13 @@
       <c r="AC9" s="5"/>
       <c r="AD9" s="5"/>
       <c r="AE9" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AF9" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AG9" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
@@ -1623,19 +1623,19 @@
       </c>
       <c r="AM9" s="5"/>
     </row>
-    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A10" s="5"/>
       <c r="B10" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>63</v>
@@ -1683,13 +1683,13 @@
       <c r="AC10" s="5"/>
       <c r="AD10" s="5"/>
       <c r="AE10" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AF10" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AG10" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
@@ -1704,19 +1704,19 @@
       </c>
       <c r="AM10" s="5"/>
     </row>
-    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A11" s="5"/>
       <c r="B11" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>63</v>
@@ -1775,19 +1775,19 @@
       <c r="AL11" s="5"/>
       <c r="AM11" s="5"/>
     </row>
-    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A12" s="5"/>
       <c r="B12" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>63</v>
@@ -1846,19 +1846,19 @@
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
     </row>
-    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A13" s="5"/>
       <c r="B13" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>63</v>
@@ -1915,19 +1915,19 @@
       <c r="AL13" s="5"/>
       <c r="AM13" s="5"/>
     </row>
-    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A14" s="5"/>
       <c r="B14" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>63</v>
@@ -1975,13 +1975,13 @@
       <c r="AC14" s="5"/>
       <c r="AD14" s="5"/>
       <c r="AE14" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AF14" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AG14" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="AH14" s="5">
         <v>1.4620299999999999</v>
@@ -2000,19 +2000,19 @@
       </c>
       <c r="AM14" s="5"/>
     </row>
-    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A15" s="5"/>
       <c r="B15" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>63</v>
@@ -2060,13 +2060,13 @@
       <c r="AC15" s="5"/>
       <c r="AD15" s="5"/>
       <c r="AE15" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AF15" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AG15" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="AH15" s="5">
         <v>1.4620299999999999</v>
@@ -2085,19 +2085,19 @@
       </c>
       <c r="AM15" s="5"/>
     </row>
-    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A16" s="5"/>
       <c r="B16" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>63</v>
@@ -2156,19 +2156,19 @@
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
     </row>
-    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A17" s="5"/>
       <c r="B17" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>63</v>
@@ -2225,19 +2225,19 @@
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
     </row>
-    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A18" s="5"/>
       <c r="B18" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D18" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>63</v>
@@ -2294,19 +2294,19 @@
       <c r="AL18" s="5"/>
       <c r="AM18" s="5"/>
     </row>
-    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A19" s="5"/>
       <c r="B19" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
@@ -2325,7 +2325,7 @@
         <v>0.3</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q19" s="5">
         <v>30</v>
@@ -2361,19 +2361,19 @@
       <c r="AL19" s="5"/>
       <c r="AM19" s="5"/>
     </row>
-    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A20" s="5"/>
       <c r="B20" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>81</v>
+        <v>151</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
@@ -2392,7 +2392,7 @@
         <v>0.3</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="Q20" s="5">
         <v>30</v>
@@ -2428,19 +2428,19 @@
       <c r="AL20" s="5"/>
       <c r="AM20" s="5"/>
     </row>
-    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A21" s="5"/>
       <c r="B21" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D21" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F21" s="5" t="s">
         <v>63</v>
@@ -2488,13 +2488,13 @@
       <c r="AC21" s="5"/>
       <c r="AD21" s="5"/>
       <c r="AE21" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AF21" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AG21" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
@@ -2509,19 +2509,19 @@
       </c>
       <c r="AM21" s="5"/>
     </row>
-    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A22" s="5"/>
       <c r="B22" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F22" s="5" t="s">
         <v>63</v>
@@ -2569,13 +2569,13 @@
       <c r="AC22" s="5"/>
       <c r="AD22" s="5"/>
       <c r="AE22" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AF22" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AG22" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
@@ -2590,19 +2590,19 @@
       </c>
       <c r="AM22" s="5"/>
     </row>
-    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A23" s="5"/>
       <c r="B23" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D23" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>63</v>
@@ -2659,19 +2659,19 @@
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
     </row>
-    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A24" s="5"/>
       <c r="B24" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D24" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>63</v>
@@ -2728,19 +2728,19 @@
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
     </row>
-    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A25" s="5"/>
       <c r="B25" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D25" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>63</v>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M25" s="5" t="s">
         <v>48</v>
@@ -2801,19 +2801,19 @@
       <c r="AL25" s="5"/>
       <c r="AM25" s="5"/>
     </row>
-    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A26" s="5"/>
       <c r="B26" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F26" s="5" t="s">
         <v>63</v>
@@ -2828,7 +2828,7 @@
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M26" s="5" t="s">
         <v>48</v>
@@ -2874,19 +2874,19 @@
       <c r="AL26" s="5"/>
       <c r="AM26" s="5"/>
     </row>
-    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A27" s="5"/>
       <c r="B27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D27" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F27" s="5" t="s">
         <v>63</v>
@@ -2943,19 +2943,19 @@
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
     </row>
-    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A28" s="5"/>
       <c r="B28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F28" s="5" t="s">
         <v>63</v>
@@ -3012,19 +3012,19 @@
       <c r="AL28" s="5"/>
       <c r="AM28" s="5"/>
     </row>
-    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="5"/>
       <c r="B29" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>63</v>
@@ -3072,13 +3072,13 @@
       <c r="AC29" s="5"/>
       <c r="AD29" s="5"/>
       <c r="AE29" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="AF29" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AG29" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="AH29" s="5"/>
       <c r="AI29" s="5"/>
@@ -3093,19 +3093,19 @@
       </c>
       <c r="AM29" s="5"/>
     </row>
-    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
@@ -3160,19 +3160,19 @@
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
     </row>
-    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A31" s="5"/>
       <c r="B31" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
@@ -3227,19 +3227,19 @@
       <c r="AL31" s="5"/>
       <c r="AM31" s="5"/>
     </row>
-    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A32" s="5"/>
       <c r="B32" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>63</v>
@@ -3287,13 +3287,13 @@
       <c r="AC32" s="5"/>
       <c r="AD32" s="5"/>
       <c r="AE32" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AF32" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AG32" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="AH32" s="5"/>
       <c r="AI32" s="5"/>
@@ -3308,19 +3308,19 @@
       </c>
       <c r="AM32" s="5"/>
     </row>
-    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A33" s="5"/>
       <c r="B33" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>63</v>
@@ -3368,13 +3368,13 @@
       <c r="AC33" s="5"/>
       <c r="AD33" s="5"/>
       <c r="AE33" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AF33" s="5" t="s">
         <v>66</v>
       </c>
       <c r="AG33" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="AH33" s="5"/>
       <c r="AI33" s="5"/>
@@ -3389,19 +3389,19 @@
       </c>
       <c r="AM33" s="5"/>
     </row>
-    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A34" s="5"/>
       <c r="B34" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>63</v>
@@ -3458,19 +3458,19 @@
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
     </row>
-    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A35" s="5"/>
       <c r="B35" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>63</v>
@@ -3527,22 +3527,22 @@
       <c r="AL35" s="5"/>
       <c r="AM35" s="5"/>
     </row>
-    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A36" s="5"/>
       <c r="B36" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5" t="s">
@@ -3598,22 +3598,22 @@
       <c r="AL36" s="5"/>
       <c r="AM36" s="5"/>
     </row>
-    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A37" s="5"/>
       <c r="B37" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5" t="s">
@@ -3669,19 +3669,19 @@
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
     </row>
-    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A38" s="5"/>
       <c r="B38" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D38" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>58</v>
@@ -3738,19 +3738,19 @@
       <c r="AL38" s="5"/>
       <c r="AM38" s="5"/>
     </row>
-    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A39" s="5"/>
       <c r="B39" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D39" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>58</v>
@@ -3807,19 +3807,19 @@
       <c r="AL39" s="5"/>
       <c r="AM39" s="5"/>
     </row>
-    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A40" s="5"/>
       <c r="B40" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
@@ -3838,7 +3838,7 @@
         <v>7000000</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="Q40" s="5">
         <v>1</v>
@@ -3874,19 +3874,19 @@
       <c r="AL40" s="5"/>
       <c r="AM40" s="5"/>
     </row>
-    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A41" s="5"/>
       <c r="B41" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
@@ -3943,19 +3943,19 @@
       <c r="AL41" s="5"/>
       <c r="AM41" s="5"/>
     </row>
-    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A42" s="5"/>
       <c r="B42" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>58</v>
@@ -4003,13 +4003,13 @@
       <c r="AC42" s="5"/>
       <c r="AD42" s="5"/>
       <c r="AE42" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AF42" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="AG42" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AH42" s="5"/>
       <c r="AI42" s="5"/>
@@ -4018,19 +4018,19 @@
       <c r="AL42" s="5"/>
       <c r="AM42" s="5"/>
     </row>
-    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
       <c r="B43" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>58</v>
@@ -4078,13 +4078,13 @@
       <c r="AC43" s="5"/>
       <c r="AD43" s="5"/>
       <c r="AE43" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AF43" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="AG43" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="AH43" s="5"/>
       <c r="AI43" s="5"/>
@@ -4093,19 +4093,19 @@
       <c r="AL43" s="5"/>
       <c r="AM43" s="5"/>
     </row>
-    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A44" s="5"/>
       <c r="B44" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
@@ -4160,19 +4160,19 @@
       <c r="AL44" s="5"/>
       <c r="AM44" s="5"/>
     </row>
-    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A45" s="5"/>
       <c r="B45" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
@@ -4229,19 +4229,19 @@
       <c r="AL45" s="5"/>
       <c r="AM45" s="5"/>
     </row>
-    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A46" s="5"/>
       <c r="B46" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
@@ -4298,19 +4298,19 @@
       <c r="AL46" s="5"/>
       <c r="AM46" s="5"/>
     </row>
-    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A47" s="5"/>
       <c r="B47" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>58</v>
@@ -4369,19 +4369,19 @@
       <c r="AL47" s="5"/>
       <c r="AM47" s="5"/>
     </row>
-    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A48" s="5"/>
       <c r="B48" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>58</v>
@@ -4440,19 +4440,19 @@
       <c r="AL48" s="5"/>
       <c r="AM48" s="5"/>
     </row>
-    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A49" s="5"/>
       <c r="B49" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
@@ -4509,19 +4509,19 @@
       <c r="AL49" s="5"/>
       <c r="AM49" s="5"/>
     </row>
-    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A50" s="5"/>
       <c r="B50" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
@@ -4576,19 +4576,19 @@
       <c r="AL50" s="5"/>
       <c r="AM50" s="5"/>
     </row>
-    <row r="51" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A51" s="5"/>
       <c r="B51" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
@@ -4643,19 +4643,19 @@
       <c r="AL51" s="5"/>
       <c r="AM51" s="5"/>
     </row>
-    <row r="52" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A52" s="5"/>
       <c r="B52" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>53</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
@@ -4710,19 +4710,19 @@
       <c r="AL52" s="5"/>
       <c r="AM52" s="5"/>
     </row>
-    <row r="53" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A53" s="5"/>
       <c r="B53" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D53" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
@@ -4777,19 +4777,19 @@
       <c r="AL53" s="5"/>
       <c r="AM53" s="5"/>
     </row>
-    <row r="54" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A54" s="5"/>
       <c r="B54" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>45</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>58</v>
@@ -4846,19 +4846,19 @@
       <c r="AL54" s="5"/>
       <c r="AM54" s="5"/>
     </row>
-    <row r="55" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A55" s="5"/>
       <c r="B55" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
@@ -4915,19 +4915,19 @@
       <c r="AL55" s="5"/>
       <c r="AM55" s="5"/>
     </row>
-    <row r="56" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A56" s="5"/>
       <c r="B56" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="D56" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>63</v>
@@ -4940,7 +4940,7 @@
       </c>
       <c r="K56" s="5"/>
       <c r="L56" s="5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M56" s="5" t="s">
         <v>48</v>
@@ -4950,7 +4950,7 @@
       </c>
       <c r="O56" s="5"/>
       <c r="P56" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="Q56" s="5">
         <v>30</v>
@@ -4965,7 +4965,7 @@
         <v>1</v>
       </c>
       <c r="U56" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="V56" s="5"/>
       <c r="W56" s="5"/>
@@ -4986,19 +4986,19 @@
       <c r="AL56" s="5"/>
       <c r="AM56" s="5"/>
     </row>
-    <row r="57" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A57" s="5"/>
       <c r="B57" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="D57" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>63</v>
@@ -5011,7 +5011,7 @@
       </c>
       <c r="K57" s="5"/>
       <c r="L57" s="5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="M57" s="5" t="s">
         <v>48</v>
@@ -5021,7 +5021,7 @@
       </c>
       <c r="O57" s="5"/>
       <c r="P57" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="Q57" s="5">
         <v>30</v>
@@ -5036,7 +5036,7 @@
         <v>1</v>
       </c>
       <c r="U57" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="V57" s="5"/>
       <c r="W57" s="5"/>
@@ -5057,19 +5057,19 @@
       <c r="AL57" s="5"/>
       <c r="AM57" s="5"/>
     </row>
-    <row r="58" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A58" s="5"/>
       <c r="B58" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>63</v>
@@ -5082,7 +5082,7 @@
       </c>
       <c r="K58" s="5"/>
       <c r="L58" s="5" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="M58" s="5" t="s">
         <v>48</v>
@@ -5092,7 +5092,7 @@
       </c>
       <c r="O58" s="5"/>
       <c r="P58" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="Q58" s="5">
         <v>7</v>
@@ -5107,7 +5107,7 @@
         <v>1</v>
       </c>
       <c r="U58" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="V58" s="5"/>
       <c r="W58" s="5"/>
@@ -5128,19 +5128,19 @@
       <c r="AL58" s="5"/>
       <c r="AM58" s="5"/>
     </row>
-    <row r="59" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A59" s="5"/>
       <c r="B59" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="D59" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>63</v>
@@ -5153,7 +5153,7 @@
       </c>
       <c r="K59" s="5"/>
       <c r="L59" s="5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="M59" s="5" t="s">
         <v>48</v>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O59" s="5"/>
       <c r="P59" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="Q59" s="5">
         <v>7</v>
@@ -5178,7 +5178,7 @@
         <v>1</v>
       </c>
       <c r="U59" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="V59" s="5"/>
       <c r="W59" s="5"/>
@@ -5199,19 +5199,19 @@
       <c r="AL59" s="5"/>
       <c r="AM59" s="5"/>
     </row>
-    <row r="60" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A60" s="5"/>
       <c r="B60" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="D60" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>63</v>
@@ -5224,7 +5224,7 @@
       </c>
       <c r="K60" s="5"/>
       <c r="L60" s="5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M60" s="5" t="s">
         <v>48</v>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="O60" s="5"/>
       <c r="P60" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="Q60" s="5">
         <v>7</v>
@@ -5243,13 +5243,13 @@
         <v>50</v>
       </c>
       <c r="S60" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="T60" s="5">
         <v>1</v>
       </c>
       <c r="U60" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="V60" s="5"/>
       <c r="W60" s="5"/>
@@ -5270,19 +5270,19 @@
       <c r="AL60" s="5"/>
       <c r="AM60" s="5"/>
     </row>
-    <row r="61" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A61" s="5"/>
       <c r="B61" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="D61" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>63</v>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="K61" s="5"/>
       <c r="L61" s="5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="M61" s="5" t="s">
         <v>48</v>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="O61" s="5"/>
       <c r="P61" s="5" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="Q61" s="5">
         <v>7</v>
@@ -5314,13 +5314,13 @@
         <v>50</v>
       </c>
       <c r="S61" s="5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="T61" s="5">
         <v>1</v>
       </c>
       <c r="U61" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="V61" s="5"/>
       <c r="W61" s="5"/>
@@ -5341,19 +5341,19 @@
       <c r="AL61" s="5"/>
       <c r="AM61" s="5"/>
     </row>
-    <row r="62" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A62" s="5"/>
       <c r="B62" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>63</v>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K62" s="5"/>
       <c r="L62" s="5" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>48</v>
@@ -5376,22 +5376,22 @@
       </c>
       <c r="O62" s="5"/>
       <c r="P62" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q62" s="5">
+        <v>1</v>
+      </c>
+      <c r="R62" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S62" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="Q62" s="5">
-        <v>1</v>
-      </c>
-      <c r="R62" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="S62" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="T62" s="5">
         <v>1</v>
       </c>
       <c r="U62" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="V62" s="5"/>
       <c r="W62" s="5"/>
@@ -5412,19 +5412,19 @@
       <c r="AL62" s="5"/>
       <c r="AM62" s="5"/>
     </row>
-    <row r="63" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A63" s="5"/>
       <c r="B63" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="D63" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>63</v>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="K63" s="5"/>
       <c r="L63" s="5" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="M63" s="5" t="s">
         <v>48</v>
@@ -5447,22 +5447,22 @@
       </c>
       <c r="O63" s="5"/>
       <c r="P63" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q63" s="5">
+        <v>1</v>
+      </c>
+      <c r="R63" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S63" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="Q63" s="5">
-        <v>1</v>
-      </c>
-      <c r="R63" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="S63" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="T63" s="5">
         <v>1</v>
       </c>
       <c r="U63" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="V63" s="5"/>
       <c r="W63" s="5"/>
@@ -5483,19 +5483,19 @@
       <c r="AL63" s="5"/>
       <c r="AM63" s="5"/>
     </row>
-    <row r="64" spans="1:39" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:39" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A64" s="5"/>
       <c r="B64" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>63</v>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="K64" s="5"/>
       <c r="L64" s="5" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="M64" s="5" t="s">
         <v>48</v>
@@ -5518,22 +5518,22 @@
       </c>
       <c r="O64" s="5"/>
       <c r="P64" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>1</v>
+      </c>
+      <c r="R64" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S64" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="Q64" s="5">
-        <v>1</v>
-      </c>
-      <c r="R64" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="S64" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="T64" s="5">
         <v>1</v>
       </c>
       <c r="U64" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="V64" s="5"/>
       <c r="W64" s="5"/>
@@ -5554,19 +5554,19 @@
       <c r="AL64" s="5"/>
       <c r="AM64" s="5"/>
     </row>
-    <row r="65" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A65" s="5"/>
       <c r="B65" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="D65" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>63</v>
@@ -5579,7 +5579,7 @@
       </c>
       <c r="K65" s="5"/>
       <c r="L65" s="5" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="M65" s="5" t="s">
         <v>48</v>
@@ -5589,22 +5589,22 @@
       </c>
       <c r="O65" s="5"/>
       <c r="P65" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="Q65" s="5">
+        <v>1</v>
+      </c>
+      <c r="R65" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S65" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="Q65" s="5">
-        <v>1</v>
-      </c>
-      <c r="R65" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="S65" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="T65" s="5">
         <v>1</v>
       </c>
       <c r="U65" s="5" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="V65" s="5"/>
       <c r="W65" s="5"/>
@@ -5625,19 +5625,19 @@
       <c r="AL65" s="5"/>
       <c r="AM65" s="5"/>
     </row>
-    <row r="66" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A66" s="5"/>
       <c r="B66" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D66" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="K66" s="5"/>
       <c r="L66" s="5" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="M66" s="5" t="s">
         <v>64</v>
@@ -5664,7 +5664,7 @@
         <v>1</v>
       </c>
       <c r="R66" s="5" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="S66" s="5" t="s">
         <v>54</v>
@@ -5685,13 +5685,13 @@
       <c r="AC66" s="5"/>
       <c r="AD66" s="5"/>
       <c r="AE66" s="5" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="AF66" s="5" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="AG66" s="5" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="AH66" s="5"/>
       <c r="AI66" s="5"/>
@@ -5712,19 +5712,19 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="67" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A67" s="5"/>
       <c r="B67" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D67" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="K67" s="5"/>
       <c r="L67" s="5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="M67" s="5" t="s">
         <v>64</v>
@@ -5751,7 +5751,7 @@
         <v>1</v>
       </c>
       <c r="R67" s="5" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="S67" s="5" t="s">
         <v>54</v>
@@ -5772,13 +5772,13 @@
       <c r="AC67" s="5"/>
       <c r="AD67" s="5"/>
       <c r="AE67" s="5" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="AF67" s="5" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="AG67" s="5" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="AH67" s="5"/>
       <c r="AI67" s="5"/>
@@ -5799,19 +5799,19 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="68" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A68" s="5"/>
       <c r="B68" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
@@ -5824,7 +5824,7 @@
       </c>
       <c r="K68" s="5"/>
       <c r="L68" s="5" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="M68" s="5" t="s">
         <v>64</v>
@@ -5859,13 +5859,13 @@
       <c r="AC68" s="5"/>
       <c r="AD68" s="5"/>
       <c r="AE68" s="5" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="AF68" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="AG68" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="AH68" s="5"/>
       <c r="AI68" s="5"/>
@@ -5874,19 +5874,19 @@
       <c r="AL68" s="5"/>
       <c r="AM68" s="5"/>
     </row>
-    <row r="69" spans="1:43" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:43" s="4" customFormat="1" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A69" s="5"/>
       <c r="B69" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="D69" s="5" t="s">
         <v>56</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
@@ -5899,7 +5899,7 @@
       </c>
       <c r="K69" s="5"/>
       <c r="L69" s="5" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="M69" s="5" t="s">
         <v>64</v>
@@ -5934,13 +5934,13 @@
       <c r="AC69" s="5"/>
       <c r="AD69" s="5"/>
       <c r="AE69" s="5" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="AF69" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="AG69" s="5" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="AH69" s="5"/>
       <c r="AI69" s="5"/>

--- a/inst/extdata/northern_cheyenne_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/northern_cheyenne_tribe_criteria_crosswalk.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FA0A469-B5C2-4040-8D3D-DDB2F3D596CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40C7AF8A-6140-45D6-A87F-6F94AD208C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E55A9BC7-10AB-4EF2-8E95-202746609CFA}"/>
+    <workbookView xWindow="28690" yWindow="-110" windowWidth="20710" windowHeight="11020" xr2:uid="{E55A9BC7-10AB-4EF2-8E95-202746609CFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="866" uniqueCount="153">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -173,9 +173,6 @@
     <t>Antimony</t>
   </si>
   <si>
-    <t>Human Health - Water + organism</t>
-  </si>
-  <si>
     <t>ANTIMONY</t>
   </si>
   <si>
@@ -197,9 +194,6 @@
     <t>n-samples in 3 years</t>
   </si>
   <si>
-    <t>Human Health - Organism</t>
-  </si>
-  <si>
     <t>arithmetic mean</t>
   </si>
   <si>
@@ -498,6 +492,9 @@
   </si>
   <si>
     <t>DISSOLVED OXYGEN</t>
+  </si>
+  <si>
+    <t>Drinking Water</t>
   </si>
 </sst>
 </file>
@@ -910,6 +907,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="24.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" s="4" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
@@ -1052,44 +1050,44 @@
         <v>44</v>
       </c>
       <c r="D2" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
       <c r="J2" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K2" s="5"/>
       <c r="L2" s="5"/>
       <c r="M2" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N2" s="5"/>
       <c r="O2" s="5">
         <v>5.6</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q2" s="5">
         <v>1</v>
       </c>
       <c r="R2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S2" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S2" s="5" t="s">
+      <c r="T2" s="5">
+        <v>1</v>
+      </c>
+      <c r="U2" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T2" s="5">
-        <v>1</v>
-      </c>
-      <c r="U2" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V2" s="5"/>
       <c r="W2" s="5"/>
@@ -1119,44 +1117,44 @@
         <v>44</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
       <c r="M3" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N3" s="5"/>
       <c r="O3" s="5">
         <v>640</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q3" s="5">
         <v>30</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T3" s="5">
         <v>1</v>
       </c>
       <c r="U3" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V3" s="5"/>
       <c r="W3" s="5"/>
@@ -1183,51 +1181,51 @@
         <v>43</v>
       </c>
       <c r="C4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I4" s="5"/>
       <c r="J4" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
       <c r="M4" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5">
         <v>340</v>
       </c>
       <c r="P4" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q4" s="5">
         <v>1</v>
       </c>
       <c r="R4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="T4" s="5">
+        <v>1</v>
+      </c>
+      <c r="U4" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T4" s="5">
-        <v>1</v>
-      </c>
-      <c r="U4" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
@@ -1254,51 +1252,51 @@
         <v>43</v>
       </c>
       <c r="C5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5">
         <v>150</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q5" s="5">
         <v>30</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T5" s="5">
         <v>1</v>
       </c>
       <c r="U5" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V5" s="5"/>
       <c r="W5" s="5"/>
@@ -1325,49 +1323,49 @@
         <v>43</v>
       </c>
       <c r="C6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
       <c r="M6" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="P6" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q6" s="5">
         <v>1</v>
       </c>
       <c r="R6" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S6" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S6" s="5" t="s">
+      <c r="T6" s="5">
+        <v>1</v>
+      </c>
+      <c r="U6" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T6" s="5">
-        <v>1</v>
-      </c>
-      <c r="U6" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V6" s="5"/>
       <c r="W6" s="5"/>
@@ -1394,49 +1392,49 @@
         <v>43</v>
       </c>
       <c r="C7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>57</v>
-      </c>
       <c r="F7" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K7" s="5"/>
       <c r="L7" s="5"/>
       <c r="M7" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5">
         <v>0.14000000000000001</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q7" s="5">
         <v>30</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T7" s="5">
         <v>1</v>
       </c>
       <c r="U7" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V7" s="5"/>
       <c r="W7" s="5"/>
@@ -1463,49 +1461,49 @@
         <v>43</v>
       </c>
       <c r="C8" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>63</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K8" s="5"/>
       <c r="L8" s="5"/>
       <c r="M8" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q8" s="5">
         <v>1</v>
       </c>
       <c r="R8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S8" s="5" t="s">
+      <c r="T8" s="5">
+        <v>1</v>
+      </c>
+      <c r="U8" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T8" s="5">
-        <v>1</v>
-      </c>
-      <c r="U8" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V8" s="5"/>
       <c r="W8" s="5"/>
@@ -1517,13 +1515,13 @@
       <c r="AC8" s="5"/>
       <c r="AD8" s="5"/>
       <c r="AE8" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AF8" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AG8" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AH8" s="5">
         <v>1.1366719999999999</v>
@@ -1548,49 +1546,49 @@
         <v>43</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I9" s="5"/>
       <c r="J9" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
       <c r="P9" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q9" s="5">
         <v>1</v>
       </c>
       <c r="R9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S9" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S9" s="5" t="s">
+      <c r="T9" s="5">
+        <v>1</v>
+      </c>
+      <c r="U9" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T9" s="5">
-        <v>1</v>
-      </c>
-      <c r="U9" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V9" s="5"/>
       <c r="W9" s="5"/>
@@ -1602,13 +1600,13 @@
       <c r="AC9" s="5"/>
       <c r="AD9" s="5"/>
       <c r="AE9" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AF9" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="AG9" s="5" t="s">
         <v>66</v>
-      </c>
-      <c r="AG9" s="5" t="s">
-        <v>68</v>
       </c>
       <c r="AH9" s="5"/>
       <c r="AI9" s="5"/>
@@ -1629,49 +1627,49 @@
         <v>43</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I10" s="5"/>
       <c r="J10" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K10" s="5"/>
       <c r="L10" s="5"/>
       <c r="M10" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N10" s="5"/>
       <c r="O10" s="5"/>
       <c r="P10" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q10" s="5">
         <v>30</v>
       </c>
       <c r="R10" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S10" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T10" s="5">
         <v>1</v>
       </c>
       <c r="U10" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V10" s="5"/>
       <c r="W10" s="5"/>
@@ -1683,13 +1681,13 @@
       <c r="AC10" s="5"/>
       <c r="AD10" s="5"/>
       <c r="AE10" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AF10" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AG10" s="5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AH10" s="5"/>
       <c r="AI10" s="5"/>
@@ -1710,51 +1708,51 @@
         <v>43</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K11" s="5"/>
       <c r="L11" s="5"/>
       <c r="M11" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5">
         <v>16</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q11" s="5">
         <v>1</v>
       </c>
       <c r="R11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S11" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S11" s="5" t="s">
+      <c r="T11" s="5">
+        <v>1</v>
+      </c>
+      <c r="U11" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T11" s="5">
-        <v>1</v>
-      </c>
-      <c r="U11" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V11" s="5"/>
       <c r="W11" s="5"/>
@@ -1781,51 +1779,51 @@
         <v>43</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K12" s="5"/>
       <c r="L12" s="5"/>
       <c r="M12" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5">
         <v>11</v>
       </c>
       <c r="P12" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q12" s="5">
         <v>30</v>
       </c>
       <c r="R12" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S12" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T12" s="5">
         <v>1</v>
       </c>
       <c r="U12" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V12" s="5"/>
       <c r="W12" s="5"/>
@@ -1852,49 +1850,49 @@
         <v>43</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
       <c r="J13" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K13" s="5"/>
       <c r="L13" s="5"/>
       <c r="M13" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5">
         <v>1300</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q13" s="5">
         <v>1</v>
       </c>
       <c r="R13" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S13" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S13" s="5" t="s">
+      <c r="T13" s="5">
+        <v>1</v>
+      </c>
+      <c r="U13" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T13" s="5">
-        <v>1</v>
-      </c>
-      <c r="U13" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V13" s="5"/>
       <c r="W13" s="5"/>
@@ -1921,49 +1919,49 @@
         <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I14" s="5"/>
       <c r="J14" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K14" s="5"/>
       <c r="L14" s="5"/>
       <c r="M14" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5"/>
       <c r="P14" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q14" s="5">
         <v>1</v>
       </c>
       <c r="R14" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S14" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S14" s="5" t="s">
+      <c r="T14" s="5">
+        <v>1</v>
+      </c>
+      <c r="U14" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T14" s="5">
-        <v>1</v>
-      </c>
-      <c r="U14" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V14" s="5"/>
       <c r="W14" s="5"/>
@@ -1975,13 +1973,13 @@
       <c r="AC14" s="5"/>
       <c r="AD14" s="5"/>
       <c r="AE14" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AF14" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AG14" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AH14" s="5">
         <v>1.4620299999999999</v>
@@ -2006,49 +2004,49 @@
         <v>43</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I15" s="5"/>
       <c r="J15" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
       <c r="M15" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5"/>
       <c r="P15" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q15" s="5">
         <v>30</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T15" s="5">
         <v>1</v>
       </c>
       <c r="U15" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V15" s="5"/>
       <c r="W15" s="5"/>
@@ -2060,13 +2058,13 @@
       <c r="AC15" s="5"/>
       <c r="AD15" s="5"/>
       <c r="AE15" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AF15" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AG15" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AH15" s="5">
         <v>1.4620299999999999</v>
@@ -2091,51 +2089,51 @@
         <v>43</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I16" s="5"/>
       <c r="J16" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K16" s="5"/>
       <c r="L16" s="5"/>
       <c r="M16" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5">
         <v>1.4</v>
       </c>
       <c r="P16" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q16" s="5">
         <v>1</v>
       </c>
       <c r="R16" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S16" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S16" s="5" t="s">
+      <c r="T16" s="5">
+        <v>1</v>
+      </c>
+      <c r="U16" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T16" s="5">
-        <v>1</v>
-      </c>
-      <c r="U16" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V16" s="5"/>
       <c r="W16" s="5"/>
@@ -2162,49 +2160,49 @@
         <v>43</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K17" s="5"/>
       <c r="L17" s="5"/>
       <c r="M17" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5">
         <v>0.05</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q17" s="5">
         <v>1</v>
       </c>
       <c r="R17" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S17" s="5" t="s">
+      <c r="T17" s="5">
+        <v>1</v>
+      </c>
+      <c r="U17" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T17" s="5">
-        <v>1</v>
-      </c>
-      <c r="U17" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V17" s="5"/>
       <c r="W17" s="5"/>
@@ -2231,49 +2229,49 @@
         <v>43</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
       <c r="J18" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K18" s="5"/>
       <c r="L18" s="5"/>
       <c r="M18" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N18" s="5"/>
       <c r="O18" s="5">
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="P18" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q18" s="5">
         <v>30</v>
       </c>
       <c r="R18" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S18" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T18" s="5">
         <v>1</v>
       </c>
       <c r="U18" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V18" s="5"/>
       <c r="W18" s="5"/>
@@ -2300,47 +2298,47 @@
         <v>43</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K19" s="5"/>
       <c r="L19" s="5"/>
       <c r="M19" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5">
         <v>0.3</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Q19" s="5">
         <v>30</v>
       </c>
       <c r="R19" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S19" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T19" s="5">
         <v>1</v>
       </c>
       <c r="U19" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V19" s="5"/>
       <c r="W19" s="5"/>
@@ -2367,47 +2365,47 @@
         <v>43</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="5"/>
       <c r="J20" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5">
         <v>0.3</v>
       </c>
       <c r="P20" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="Q20" s="5">
         <v>30</v>
       </c>
       <c r="R20" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S20" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T20" s="5">
         <v>1</v>
       </c>
       <c r="U20" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V20" s="5"/>
       <c r="W20" s="5"/>
@@ -2434,49 +2432,49 @@
         <v>43</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I21" s="5"/>
       <c r="J21" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K21" s="5"/>
       <c r="L21" s="5"/>
       <c r="M21" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5"/>
       <c r="P21" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q21" s="5">
         <v>1</v>
       </c>
       <c r="R21" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S21" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S21" s="5" t="s">
+      <c r="T21" s="5">
+        <v>1</v>
+      </c>
+      <c r="U21" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T21" s="5">
-        <v>1</v>
-      </c>
-      <c r="U21" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V21" s="5"/>
       <c r="W21" s="5"/>
@@ -2488,13 +2486,13 @@
       <c r="AC21" s="5"/>
       <c r="AD21" s="5"/>
       <c r="AE21" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AF21" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AG21" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="AH21" s="5"/>
       <c r="AI21" s="5"/>
@@ -2515,49 +2513,49 @@
         <v>43</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I22" s="5"/>
       <c r="J22" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5"/>
       <c r="P22" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q22" s="5">
         <v>30</v>
       </c>
       <c r="R22" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S22" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T22" s="5">
         <v>1</v>
       </c>
       <c r="U22" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V22" s="5"/>
       <c r="W22" s="5"/>
@@ -2569,13 +2567,13 @@
       <c r="AC22" s="5"/>
       <c r="AD22" s="5"/>
       <c r="AE22" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AF22" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AG22" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AH22" s="5"/>
       <c r="AI22" s="5"/>
@@ -2596,49 +2594,49 @@
         <v>43</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5"/>
       <c r="I23" s="5"/>
       <c r="J23" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
       <c r="M23" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5">
         <v>610</v>
       </c>
       <c r="P23" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q23" s="5">
         <v>1</v>
       </c>
       <c r="R23" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S23" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S23" s="5" t="s">
+      <c r="T23" s="5">
+        <v>1</v>
+      </c>
+      <c r="U23" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T23" s="5">
-        <v>1</v>
-      </c>
-      <c r="U23" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V23" s="5"/>
       <c r="W23" s="5"/>
@@ -2665,49 +2663,49 @@
         <v>43</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="5"/>
       <c r="I24" s="5"/>
       <c r="J24" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
       <c r="M24" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N24" s="5"/>
       <c r="O24" s="5">
         <v>4600</v>
       </c>
       <c r="P24" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q24" s="5">
         <v>30</v>
       </c>
       <c r="R24" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S24" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T24" s="5">
         <v>1</v>
       </c>
       <c r="U24" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V24" s="5"/>
       <c r="W24" s="5"/>
@@ -2734,53 +2732,53 @@
         <v>43</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I25" s="5"/>
       <c r="J25" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K25" s="5"/>
       <c r="L25" s="5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="M25" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5">
         <v>1.5</v>
       </c>
       <c r="P25" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q25" s="5">
         <v>30</v>
       </c>
       <c r="R25" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S25" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T25" s="5">
         <v>1</v>
       </c>
       <c r="U25" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V25" s="5"/>
       <c r="W25" s="5"/>
@@ -2807,53 +2805,53 @@
         <v>43</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I26" s="5"/>
       <c r="J26" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K26" s="5"/>
       <c r="L26" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="M26" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N26" s="5"/>
       <c r="O26" s="5">
         <v>3.1</v>
       </c>
       <c r="P26" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q26" s="5">
         <v>30</v>
       </c>
       <c r="R26" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S26" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T26" s="5">
         <v>1</v>
       </c>
       <c r="U26" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V26" s="5"/>
       <c r="W26" s="5"/>
@@ -2880,49 +2878,49 @@
         <v>43</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
       <c r="I27" s="5"/>
       <c r="J27" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
       <c r="M27" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5">
         <v>170</v>
       </c>
       <c r="P27" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q27" s="5">
         <v>1</v>
       </c>
       <c r="R27" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S27" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S27" s="5" t="s">
+      <c r="T27" s="5">
+        <v>1</v>
+      </c>
+      <c r="U27" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T27" s="5">
-        <v>1</v>
-      </c>
-      <c r="U27" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V27" s="5"/>
       <c r="W27" s="5"/>
@@ -2949,49 +2947,49 @@
         <v>43</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
       <c r="M28" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5">
         <v>4200</v>
       </c>
       <c r="P28" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q28" s="5">
         <v>30</v>
       </c>
       <c r="R28" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S28" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T28" s="5">
         <v>1</v>
       </c>
       <c r="U28" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V28" s="5"/>
       <c r="W28" s="5"/>
@@ -3018,49 +3016,49 @@
         <v>43</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I29" s="5"/>
       <c r="J29" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K29" s="5"/>
       <c r="L29" s="5"/>
       <c r="M29" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
       <c r="P29" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q29" s="5">
         <v>1</v>
       </c>
       <c r="R29" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S29" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S29" s="5" t="s">
+      <c r="T29" s="5">
+        <v>1</v>
+      </c>
+      <c r="U29" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T29" s="5">
-        <v>1</v>
-      </c>
-      <c r="U29" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V29" s="5"/>
       <c r="W29" s="5"/>
@@ -3072,13 +3070,13 @@
       <c r="AC29" s="5"/>
       <c r="AD29" s="5"/>
       <c r="AE29" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AF29" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AG29" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AH29" s="5"/>
       <c r="AI29" s="5"/>
@@ -3099,47 +3097,47 @@
         <v>43</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K30" s="5"/>
       <c r="L30" s="5"/>
       <c r="M30" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5">
         <v>0.24</v>
       </c>
       <c r="P30" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q30" s="5">
         <v>1</v>
       </c>
       <c r="R30" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S30" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S30" s="5" t="s">
+      <c r="T30" s="5">
+        <v>1</v>
+      </c>
+      <c r="U30" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T30" s="5">
-        <v>1</v>
-      </c>
-      <c r="U30" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V30" s="5"/>
       <c r="W30" s="5"/>
@@ -3166,47 +3164,47 @@
         <v>43</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="5"/>
       <c r="J31" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K31" s="5"/>
       <c r="L31" s="5"/>
       <c r="M31" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N31" s="5"/>
       <c r="O31" s="5">
         <v>0.47</v>
       </c>
       <c r="P31" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q31" s="5">
         <v>30</v>
       </c>
       <c r="R31" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S31" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T31" s="5">
         <v>1</v>
       </c>
       <c r="U31" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V31" s="5"/>
       <c r="W31" s="5"/>
@@ -3233,49 +3231,49 @@
         <v>43</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I32" s="5"/>
       <c r="J32" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K32" s="5"/>
       <c r="L32" s="5"/>
       <c r="M32" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N32" s="5"/>
       <c r="O32" s="5"/>
       <c r="P32" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q32" s="5">
         <v>1</v>
       </c>
       <c r="R32" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S32" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S32" s="5" t="s">
+      <c r="T32" s="5">
+        <v>1</v>
+      </c>
+      <c r="U32" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T32" s="5">
-        <v>1</v>
-      </c>
-      <c r="U32" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V32" s="5"/>
       <c r="W32" s="5"/>
@@ -3287,13 +3285,13 @@
       <c r="AC32" s="5"/>
       <c r="AD32" s="5"/>
       <c r="AE32" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AF32" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AG32" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AH32" s="5"/>
       <c r="AI32" s="5"/>
@@ -3314,49 +3312,49 @@
         <v>43</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I33" s="5"/>
       <c r="J33" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K33" s="5"/>
       <c r="L33" s="5"/>
       <c r="M33" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5"/>
       <c r="P33" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q33" s="5">
         <v>30</v>
       </c>
       <c r="R33" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S33" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T33" s="5">
         <v>1</v>
       </c>
       <c r="U33" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V33" s="5"/>
       <c r="W33" s="5"/>
@@ -3368,13 +3366,13 @@
       <c r="AC33" s="5"/>
       <c r="AD33" s="5"/>
       <c r="AE33" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AF33" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="AG33" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="AH33" s="5"/>
       <c r="AI33" s="5"/>
@@ -3395,49 +3393,49 @@
         <v>43</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="5"/>
       <c r="J34" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="5">
         <v>7400</v>
       </c>
       <c r="P34" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q34" s="5">
         <v>1</v>
       </c>
       <c r="R34" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S34" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S34" s="5" t="s">
+      <c r="T34" s="5">
+        <v>1</v>
+      </c>
+      <c r="U34" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T34" s="5">
-        <v>1</v>
-      </c>
-      <c r="U34" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V34" s="5"/>
       <c r="W34" s="5"/>
@@ -3464,49 +3462,49 @@
         <v>43</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="5"/>
       <c r="J35" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K35" s="5"/>
       <c r="L35" s="5"/>
       <c r="M35" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N35" s="5"/>
       <c r="O35" s="5">
         <v>26000</v>
       </c>
       <c r="P35" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q35" s="5">
         <v>30</v>
       </c>
       <c r="R35" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S35" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T35" s="5">
         <v>1</v>
       </c>
       <c r="U35" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V35" s="5"/>
       <c r="W35" s="5"/>
@@ -3533,51 +3531,51 @@
         <v>43</v>
       </c>
       <c r="C36" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F36" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I36" s="5"/>
       <c r="J36" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K36" s="5"/>
       <c r="L36" s="5"/>
       <c r="M36" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5">
         <v>22</v>
       </c>
       <c r="P36" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q36" s="5">
         <v>1</v>
       </c>
       <c r="R36" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S36" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S36" s="5" t="s">
+      <c r="T36" s="5">
+        <v>1</v>
+      </c>
+      <c r="U36" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T36" s="5">
-        <v>1</v>
-      </c>
-      <c r="U36" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V36" s="5"/>
       <c r="W36" s="5"/>
@@ -3604,51 +3602,51 @@
         <v>43</v>
       </c>
       <c r="C37" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F37" s="5" t="s">
         <v>99</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>101</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I37" s="5"/>
       <c r="J37" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N37" s="5"/>
       <c r="O37" s="5">
         <v>5.2</v>
       </c>
       <c r="P37" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q37" s="5">
         <v>30</v>
       </c>
       <c r="R37" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S37" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T37" s="5">
         <v>1</v>
       </c>
       <c r="U37" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V37" s="5"/>
       <c r="W37" s="5"/>
@@ -3675,49 +3673,49 @@
         <v>43</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="5"/>
       <c r="J38" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N38" s="5"/>
       <c r="O38" s="5">
         <v>4</v>
       </c>
       <c r="P38" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q38" s="5">
         <v>1</v>
       </c>
       <c r="R38" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S38" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S38" s="5" t="s">
+      <c r="T38" s="5">
+        <v>1</v>
+      </c>
+      <c r="U38" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T38" s="5">
-        <v>1</v>
-      </c>
-      <c r="U38" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V38" s="5"/>
       <c r="W38" s="5"/>
@@ -3744,49 +3742,49 @@
         <v>43</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="5"/>
       <c r="J39" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K39" s="5"/>
       <c r="L39" s="5"/>
       <c r="M39" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N39" s="5"/>
       <c r="O39" s="5">
         <v>400</v>
       </c>
       <c r="P39" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q39" s="5">
         <v>30</v>
       </c>
       <c r="R39" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S39" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T39" s="5">
         <v>1</v>
       </c>
       <c r="U39" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V39" s="5"/>
       <c r="W39" s="5"/>
@@ -3813,47 +3811,47 @@
         <v>43</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N40" s="5"/>
       <c r="O40" s="5">
         <v>7000000</v>
       </c>
       <c r="P40" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="Q40" s="5">
         <v>1</v>
       </c>
       <c r="R40" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S40" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S40" s="5" t="s">
+      <c r="T40" s="5">
+        <v>1</v>
+      </c>
+      <c r="U40" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T40" s="5">
-        <v>1</v>
-      </c>
-      <c r="U40" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V40" s="5"/>
       <c r="W40" s="5"/>
@@ -3880,49 +3878,49 @@
         <v>43</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I41" s="5"/>
       <c r="J41" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K41" s="5"/>
       <c r="L41" s="5"/>
       <c r="M41" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N41" s="5"/>
       <c r="O41" s="5">
         <v>20000</v>
       </c>
       <c r="P41" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q41" s="5">
         <v>30</v>
       </c>
       <c r="R41" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S41" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T41" s="5">
         <v>1</v>
       </c>
       <c r="U41" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V41" s="5"/>
       <c r="W41" s="5"/>
@@ -3949,49 +3947,49 @@
         <v>43</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D42" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F42" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F42" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I42" s="5"/>
       <c r="J42" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K42" s="5"/>
       <c r="L42" s="5"/>
       <c r="M42" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N42" s="5"/>
       <c r="O42" s="5"/>
       <c r="P42" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q42" s="5">
         <v>1</v>
       </c>
       <c r="R42" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S42" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S42" s="5" t="s">
+      <c r="T42" s="5">
+        <v>1</v>
+      </c>
+      <c r="U42" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T42" s="5">
-        <v>1</v>
-      </c>
-      <c r="U42" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V42" s="5"/>
       <c r="W42" s="5"/>
@@ -4003,13 +4001,13 @@
       <c r="AC42" s="5"/>
       <c r="AD42" s="5"/>
       <c r="AE42" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF42" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG42" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AH42" s="5"/>
       <c r="AI42" s="5"/>
@@ -4024,49 +4022,49 @@
         <v>43</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D43" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E43" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F43" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N43" s="5"/>
       <c r="O43" s="5"/>
       <c r="P43" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q43" s="5">
         <v>30</v>
       </c>
       <c r="R43" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S43" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T43" s="5">
         <v>1</v>
       </c>
       <c r="U43" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V43" s="5"/>
       <c r="W43" s="5"/>
@@ -4078,13 +4076,13 @@
       <c r="AC43" s="5"/>
       <c r="AD43" s="5"/>
       <c r="AE43" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AF43" s="5" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="AG43" s="5" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AH43" s="5"/>
       <c r="AI43" s="5"/>
@@ -4099,47 +4097,47 @@
         <v>43</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="5"/>
       <c r="J44" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K44" s="5"/>
       <c r="L44" s="5"/>
       <c r="M44" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N44" s="5"/>
       <c r="O44" s="5">
         <v>1000</v>
       </c>
       <c r="P44" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q44" s="5">
         <v>1</v>
       </c>
       <c r="R44" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S44" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S44" s="5" t="s">
+      <c r="T44" s="5">
+        <v>1</v>
+      </c>
+      <c r="U44" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T44" s="5">
-        <v>1</v>
-      </c>
-      <c r="U44" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V44" s="5"/>
       <c r="W44" s="5"/>
@@ -4166,49 +4164,49 @@
         <v>43</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I45" s="5"/>
       <c r="J45" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K45" s="5"/>
       <c r="L45" s="5"/>
       <c r="M45" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N45" s="5"/>
       <c r="O45" s="5">
         <v>860000</v>
       </c>
       <c r="P45" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q45" s="5">
         <v>1</v>
       </c>
       <c r="R45" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S45" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S45" s="5" t="s">
+      <c r="T45" s="5">
+        <v>1</v>
+      </c>
+      <c r="U45" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T45" s="5">
-        <v>1</v>
-      </c>
-      <c r="U45" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V45" s="5"/>
       <c r="W45" s="5"/>
@@ -4235,49 +4233,49 @@
         <v>43</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I46" s="5"/>
       <c r="J46" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
       <c r="M46" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N46" s="5"/>
       <c r="O46" s="5">
         <v>230000</v>
       </c>
       <c r="P46" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q46" s="5">
         <v>30</v>
       </c>
       <c r="R46" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S46" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T46" s="5">
         <v>1</v>
       </c>
       <c r="U46" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V46" s="5"/>
       <c r="W46" s="5"/>
@@ -4304,51 +4302,51 @@
         <v>43</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D47" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E47" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I47" s="5"/>
       <c r="J47" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N47" s="5"/>
       <c r="O47" s="5">
         <v>19</v>
       </c>
       <c r="P47" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q47" s="5">
         <v>1</v>
       </c>
       <c r="R47" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S47" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S47" s="5" t="s">
+      <c r="T47" s="5">
+        <v>1</v>
+      </c>
+      <c r="U47" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T47" s="5">
-        <v>1</v>
-      </c>
-      <c r="U47" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V47" s="5"/>
       <c r="W47" s="5"/>
@@ -4375,51 +4373,51 @@
         <v>43</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D48" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
       <c r="M48" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N48" s="5"/>
       <c r="O48" s="5">
         <v>11</v>
       </c>
       <c r="P48" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q48" s="5">
         <v>30</v>
       </c>
       <c r="R48" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S48" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T48" s="5">
         <v>1</v>
       </c>
       <c r="U48" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V48" s="5"/>
       <c r="W48" s="5"/>
@@ -4446,49 +4444,49 @@
         <v>43</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I49" s="5"/>
       <c r="J49" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K49" s="5"/>
       <c r="L49" s="5"/>
       <c r="M49" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N49" s="5"/>
       <c r="O49" s="5">
         <v>1000</v>
       </c>
       <c r="P49" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q49" s="5">
         <v>30</v>
       </c>
       <c r="R49" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S49" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T49" s="5">
         <v>1</v>
       </c>
       <c r="U49" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V49" s="5"/>
       <c r="W49" s="5"/>
@@ -4515,47 +4513,47 @@
         <v>43</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N50" s="5"/>
       <c r="O50" s="5">
         <v>300</v>
       </c>
       <c r="P50" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q50" s="5">
         <v>1</v>
       </c>
       <c r="R50" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S50" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S50" s="5" t="s">
+      <c r="T50" s="5">
+        <v>1</v>
+      </c>
+      <c r="U50" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T50" s="5">
-        <v>1</v>
-      </c>
-      <c r="U50" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V50" s="5"/>
       <c r="W50" s="5"/>
@@ -4582,47 +4580,47 @@
         <v>43</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K51" s="5"/>
       <c r="L51" s="5"/>
       <c r="M51" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N51" s="5"/>
       <c r="O51" s="5">
         <v>50</v>
       </c>
       <c r="P51" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q51" s="5">
         <v>1</v>
       </c>
       <c r="R51" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S51" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S51" s="5" t="s">
+      <c r="T51" s="5">
+        <v>1</v>
+      </c>
+      <c r="U51" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T51" s="5">
-        <v>1</v>
-      </c>
-      <c r="U51" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V51" s="5"/>
       <c r="W51" s="5"/>
@@ -4649,47 +4647,47 @@
         <v>43</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K52" s="5"/>
       <c r="L52" s="5"/>
       <c r="M52" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N52" s="5"/>
       <c r="O52" s="5">
         <v>100</v>
       </c>
       <c r="P52" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q52" s="5">
         <v>30</v>
       </c>
       <c r="R52" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S52" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T52" s="5">
         <v>1</v>
       </c>
       <c r="U52" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V52" s="5"/>
       <c r="W52" s="5"/>
@@ -4716,47 +4714,47 @@
         <v>43</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="5"/>
       <c r="J53" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K53" s="5"/>
       <c r="L53" s="5"/>
       <c r="M53" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N53" s="5"/>
       <c r="O53" s="5">
         <v>10000</v>
       </c>
       <c r="P53" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q53" s="5">
         <v>1</v>
       </c>
       <c r="R53" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S53" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S53" s="5" t="s">
+      <c r="T53" s="5">
+        <v>1</v>
+      </c>
+      <c r="U53" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T53" s="5">
-        <v>1</v>
-      </c>
-      <c r="U53" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V53" s="5"/>
       <c r="W53" s="5"/>
@@ -4783,49 +4781,49 @@
         <v>43</v>
       </c>
       <c r="C54" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="D54" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="E54" s="5" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
       <c r="J54" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N54" s="5"/>
       <c r="O54" s="5">
         <v>250000</v>
       </c>
       <c r="P54" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q54" s="5">
         <v>1</v>
       </c>
       <c r="R54" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="S54" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S54" s="5" t="s">
+      <c r="T54" s="5">
+        <v>1</v>
+      </c>
+      <c r="U54" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="T54" s="5">
-        <v>1</v>
-      </c>
-      <c r="U54" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="V54" s="5"/>
       <c r="W54" s="5"/>
@@ -4852,49 +4850,49 @@
         <v>43</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
       <c r="H55" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I55" s="5"/>
       <c r="J55" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N55" s="5"/>
       <c r="O55" s="5">
         <v>2</v>
       </c>
       <c r="P55" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q55" s="5">
         <v>30</v>
       </c>
       <c r="R55" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S55" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T55" s="5">
         <v>1</v>
       </c>
       <c r="U55" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V55" s="5"/>
       <c r="W55" s="5"/>
@@ -4921,51 +4919,51 @@
         <v>43</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="5"/>
       <c r="J56" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K56" s="5"/>
       <c r="L56" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M56" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N56" s="5">
         <v>6.5</v>
       </c>
       <c r="O56" s="5"/>
       <c r="P56" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q56" s="5">
         <v>30</v>
       </c>
       <c r="R56" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S56" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T56" s="5">
         <v>1</v>
       </c>
       <c r="U56" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="V56" s="5"/>
       <c r="W56" s="5"/>
@@ -4992,51 +4990,51 @@
         <v>43</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="5"/>
       <c r="J57" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K57" s="5"/>
       <c r="L57" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M57" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N57" s="5">
         <v>5.5</v>
       </c>
       <c r="O57" s="5"/>
       <c r="P57" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q57" s="5">
         <v>30</v>
       </c>
       <c r="R57" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S57" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T57" s="5">
         <v>1</v>
       </c>
       <c r="U57" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="V57" s="5"/>
       <c r="W57" s="5"/>
@@ -5063,51 +5061,51 @@
         <v>43</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="5"/>
       <c r="J58" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K58" s="5"/>
       <c r="L58" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M58" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N58" s="5">
         <v>9.5</v>
       </c>
       <c r="O58" s="5"/>
       <c r="P58" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q58" s="5">
         <v>7</v>
       </c>
       <c r="R58" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S58" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T58" s="5">
         <v>1</v>
       </c>
       <c r="U58" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="V58" s="5"/>
       <c r="W58" s="5"/>
@@ -5134,51 +5132,51 @@
         <v>43</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
       <c r="J59" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K59" s="5"/>
       <c r="L59" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M59" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N59" s="5">
         <v>6</v>
       </c>
       <c r="O59" s="5"/>
       <c r="P59" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q59" s="5">
         <v>7</v>
       </c>
       <c r="R59" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S59" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T59" s="5">
         <v>1</v>
       </c>
       <c r="U59" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="V59" s="5"/>
       <c r="W59" s="5"/>
@@ -5205,51 +5203,51 @@
         <v>43</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K60" s="5"/>
       <c r="L60" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M60" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N60" s="5">
         <v>5</v>
       </c>
       <c r="O60" s="5"/>
       <c r="P60" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q60" s="5">
         <v>7</v>
       </c>
       <c r="R60" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S60" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T60" s="5">
         <v>1</v>
       </c>
       <c r="U60" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="V60" s="5"/>
       <c r="W60" s="5"/>
@@ -5276,51 +5274,51 @@
         <v>43</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="5"/>
       <c r="J61" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K61" s="5"/>
       <c r="L61" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M61" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N61" s="5">
         <v>4</v>
       </c>
       <c r="O61" s="5"/>
       <c r="P61" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q61" s="5">
         <v>7</v>
       </c>
       <c r="R61" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S61" s="5" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="T61" s="5">
         <v>1</v>
       </c>
       <c r="U61" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="V61" s="5"/>
       <c r="W61" s="5"/>
@@ -5347,51 +5345,51 @@
         <v>43</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="5"/>
       <c r="J62" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K62" s="5"/>
       <c r="L62" s="5" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M62" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N62" s="5">
         <v>8</v>
       </c>
       <c r="O62" s="5"/>
       <c r="P62" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q62" s="5">
         <v>1</v>
       </c>
       <c r="R62" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S62" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T62" s="5">
         <v>1</v>
       </c>
       <c r="U62" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="V62" s="5"/>
       <c r="W62" s="5"/>
@@ -5418,51 +5416,51 @@
         <v>43</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="5"/>
       <c r="J63" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K63" s="5"/>
       <c r="L63" s="5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="M63" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N63" s="5">
         <v>5</v>
       </c>
       <c r="O63" s="5"/>
       <c r="P63" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q63" s="5">
         <v>1</v>
       </c>
       <c r="R63" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S63" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T63" s="5">
         <v>1</v>
       </c>
       <c r="U63" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="V63" s="5"/>
       <c r="W63" s="5"/>
@@ -5489,51 +5487,51 @@
         <v>43</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="5"/>
       <c r="J64" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K64" s="5"/>
       <c r="L64" s="5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M64" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N64" s="5">
         <v>4</v>
       </c>
       <c r="O64" s="5"/>
       <c r="P64" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q64" s="5">
         <v>1</v>
       </c>
       <c r="R64" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S64" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T64" s="5">
         <v>1</v>
       </c>
       <c r="U64" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="V64" s="5"/>
       <c r="W64" s="5"/>
@@ -5560,51 +5558,51 @@
         <v>43</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="5"/>
       <c r="J65" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K65" s="5"/>
       <c r="L65" s="5" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="M65" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N65" s="5">
         <v>3</v>
       </c>
       <c r="O65" s="5"/>
       <c r="P65" s="5" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="Q65" s="5">
         <v>1</v>
       </c>
       <c r="R65" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S65" s="5" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="T65" s="5">
         <v>1</v>
       </c>
       <c r="U65" s="5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="V65" s="5"/>
       <c r="W65" s="5"/>
@@ -5631,49 +5629,49 @@
         <v>43</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D66" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F66" s="5"/>
       <c r="G66" s="5"/>
       <c r="H66" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I66" s="5"/>
       <c r="J66" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K66" s="5"/>
       <c r="L66" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M66" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N66" s="5"/>
       <c r="O66" s="5"/>
       <c r="P66" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q66" s="5">
         <v>1</v>
       </c>
       <c r="R66" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="S66" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T66" s="5">
         <v>1</v>
       </c>
       <c r="U66" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V66" s="5"/>
       <c r="W66" s="5"/>
@@ -5685,13 +5683,13 @@
       <c r="AC66" s="5"/>
       <c r="AD66" s="5"/>
       <c r="AE66" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AF66" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG66" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AH66" s="5"/>
       <c r="AI66" s="5"/>
@@ -5718,49 +5716,49 @@
         <v>43</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D67" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F67" s="5"/>
       <c r="G67" s="5"/>
       <c r="H67" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="I67" s="5"/>
       <c r="J67" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K67" s="5"/>
       <c r="L67" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="M67" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N67" s="5"/>
       <c r="O67" s="5"/>
       <c r="P67" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q67" s="5">
         <v>1</v>
       </c>
       <c r="R67" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="S67" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T67" s="5">
         <v>1</v>
       </c>
       <c r="U67" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V67" s="5"/>
       <c r="W67" s="5"/>
@@ -5772,13 +5770,13 @@
       <c r="AC67" s="5"/>
       <c r="AD67" s="5"/>
       <c r="AE67" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AF67" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="AG67" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="AG67" s="5" t="s">
-        <v>141</v>
       </c>
       <c r="AH67" s="5"/>
       <c r="AI67" s="5"/>
@@ -5805,49 +5803,49 @@
         <v>43</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D68" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F68" s="5"/>
       <c r="G68" s="5"/>
       <c r="H68" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I68" s="5"/>
       <c r="J68" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K68" s="5"/>
       <c r="L68" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M68" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N68" s="5"/>
       <c r="O68" s="5"/>
       <c r="P68" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q68" s="5">
         <v>30</v>
       </c>
       <c r="R68" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S68" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T68" s="5">
         <v>1</v>
       </c>
       <c r="U68" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V68" s="5"/>
       <c r="W68" s="5"/>
@@ -5859,13 +5857,13 @@
       <c r="AC68" s="5"/>
       <c r="AD68" s="5"/>
       <c r="AE68" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="AF68" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="AG68" s="5" t="s">
         <v>143</v>
-      </c>
-      <c r="AF68" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="AG68" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="AH68" s="5"/>
       <c r="AI68" s="5"/>
@@ -5880,49 +5878,49 @@
         <v>43</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D69" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F69" s="5"/>
       <c r="G69" s="5"/>
       <c r="H69" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I69" s="5"/>
       <c r="J69" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K69" s="5"/>
       <c r="L69" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M69" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="N69" s="5"/>
       <c r="O69" s="5"/>
       <c r="P69" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q69" s="5">
         <v>30</v>
       </c>
       <c r="R69" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="S69" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="T69" s="5">
         <v>1</v>
       </c>
       <c r="U69" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="V69" s="5"/>
       <c r="W69" s="5"/>
@@ -5934,13 +5932,13 @@
       <c r="AC69" s="5"/>
       <c r="AD69" s="5"/>
       <c r="AE69" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AF69" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="AG69" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AH69" s="5"/>
       <c r="AI69" s="5"/>

--- a/inst/extdata/northern_cheyenne_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/northern_cheyenne_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/sheila_saia_tetratech_com/Documents/Documents/github/TADACommunityHub/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{40C7AF8A-6140-45D6-A87F-6F94AD208C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{305A89A9-991C-47A1-8CBC-EE80B67D0158}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67033712-198A-4757-B500-AE2A7181765C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E55A9BC7-10AB-4EF2-8E95-202746609CFA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{E55A9BC7-10AB-4EF2-8E95-202746609CFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,9 +131,6 @@
     <t>EquationType</t>
   </si>
   <si>
-    <t>Equation</t>
-  </si>
-  <si>
     <t>hardness_param_1</t>
   </si>
   <si>
@@ -486,6 +483,9 @@
   </si>
   <si>
     <t>0.986*e^(0.8473*(ln(hardness))+0.884)</t>
+  </si>
+  <si>
+    <t>EquationFormula</t>
   </si>
 </sst>
 </file>
@@ -995,86 +995,86 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="AI1" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" s="1" t="s">
+      <c r="AL1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" s="1" t="s">
+      <c r="AM1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
+      <c r="AN1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" s="1" t="s">
+      <c r="AO1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3">
         <v>5.6</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q2" s="3">
         <v>1</v>
       </c>
       <c r="R2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="3">
+        <v>1</v>
+      </c>
+      <c r="U2" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T2" s="3">
-        <v>1</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -1097,50 +1097,50 @@
     <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>44</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3">
         <v>640</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q3" s="3">
         <v>30</v>
       </c>
       <c r="R3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S3" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T3" s="3">
         <v>1</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -1163,54 +1163,54 @@
     <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3">
         <v>340</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q4" s="3">
         <v>1</v>
       </c>
       <c r="R4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S4" s="3" t="s">
+      <c r="T4" s="3">
+        <v>1</v>
+      </c>
+      <c r="U4" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T4" s="3">
-        <v>1</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1233,54 +1233,54 @@
     <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3">
         <v>150</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q5" s="3">
         <v>30</v>
       </c>
       <c r="R5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S5" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T5" s="3">
         <v>1</v>
       </c>
       <c r="U5" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -1303,52 +1303,52 @@
     <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q6" s="3">
         <v>1</v>
       </c>
       <c r="R6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S6" s="3" t="s">
+      <c r="T6" s="3">
+        <v>1</v>
+      </c>
+      <c r="U6" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T6" s="3">
-        <v>1</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -1371,52 +1371,52 @@
     <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3">
         <v>0.14000000000000001</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q7" s="3">
         <v>30</v>
       </c>
       <c r="R7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S7" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T7" s="3">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -1439,52 +1439,52 @@
     <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E8" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q8" s="3">
         <v>1</v>
       </c>
       <c r="R8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S8" s="3" t="s">
+      <c r="T8" s="3">
+        <v>1</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -1496,10 +1496,10 @@
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG8" s="3">
         <v>1.1366719999999999</v>
@@ -1521,52 +1521,52 @@
     <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q9" s="3">
         <v>1</v>
       </c>
       <c r="R9" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="T9" s="3">
+        <v>1</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -1578,10 +1578,10 @@
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
@@ -1599,52 +1599,52 @@
     <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q10" s="3">
         <v>30</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T10" s="3">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -1656,10 +1656,10 @@
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AF10" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
@@ -1677,54 +1677,54 @@
     <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3">
         <v>16</v>
       </c>
       <c r="P11" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q11" s="3">
         <v>1</v>
       </c>
       <c r="R11" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S11" s="3" t="s">
+      <c r="T11" s="3">
+        <v>1</v>
+      </c>
+      <c r="U11" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T11" s="3">
-        <v>1</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -1747,54 +1747,54 @@
     <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3">
         <v>11</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q12" s="3">
         <v>30</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T12" s="3">
         <v>1</v>
       </c>
       <c r="U12" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -1817,52 +1817,52 @@
     <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>66</v>
-      </c>
       <c r="F13" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3">
         <v>1300</v>
       </c>
       <c r="P13" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q13" s="3">
         <v>1</v>
       </c>
       <c r="R13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S13" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S13" s="3" t="s">
+      <c r="T13" s="3">
+        <v>1</v>
+      </c>
+      <c r="U13" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T13" s="3">
-        <v>1</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -1885,52 +1885,52 @@
     <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q14" s="3">
         <v>1</v>
       </c>
       <c r="R14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3">
+        <v>1</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T14" s="3">
-        <v>1</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -1942,10 +1942,10 @@
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AF14" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AG14" s="3">
         <v>1.4620299999999999</v>
@@ -1967,52 +1967,52 @@
     <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>68</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q15" s="3">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T15" s="3">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -2024,10 +2024,10 @@
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG15" s="3">
         <v>1.4620299999999999</v>
@@ -2049,54 +2049,54 @@
     <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="F16" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3">
         <v>1.4</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q16" s="3">
         <v>1</v>
       </c>
       <c r="R16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S16" s="3" t="s">
+      <c r="T16" s="3">
+        <v>1</v>
+      </c>
+      <c r="U16" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T16" s="3">
-        <v>1</v>
-      </c>
-      <c r="U16" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -2119,52 +2119,52 @@
     <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3">
         <v>0.05</v>
       </c>
       <c r="P17" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q17" s="3">
         <v>1</v>
       </c>
       <c r="R17" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S17" s="3" t="s">
+      <c r="T17" s="3">
+        <v>1</v>
+      </c>
+      <c r="U17" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -2187,52 +2187,52 @@
     <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3">
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q18" s="3">
         <v>30</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T18" s="3">
         <v>1</v>
       </c>
       <c r="U18" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2255,50 +2255,50 @@
     <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3">
         <v>0.3</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q19" s="3">
         <v>30</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S19" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T19" s="3">
         <v>1</v>
       </c>
       <c r="U19" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2321,50 +2321,50 @@
     <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3">
         <v>0.3</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q20" s="3">
         <v>30</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S20" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T20" s="3">
         <v>1</v>
       </c>
       <c r="U20" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2387,52 +2387,52 @@
     <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="F21" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q21" s="3">
         <v>1</v>
       </c>
       <c r="R21" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S21" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S21" s="3" t="s">
+      <c r="T21" s="3">
+        <v>1</v>
+      </c>
+      <c r="U21" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T21" s="3">
-        <v>1</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2444,10 +2444,10 @@
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AF21" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AG21" s="3"/>
       <c r="AH21" s="3"/>
@@ -2465,52 +2465,52 @@
     <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="F22" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q22" s="3">
         <v>30</v>
       </c>
       <c r="R22" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S22" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T22" s="3">
         <v>1</v>
       </c>
       <c r="U22" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2522,10 +2522,10 @@
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AF22" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="AG22" s="3"/>
       <c r="AH22" s="3"/>
@@ -2543,52 +2543,52 @@
     <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3">
         <v>610</v>
       </c>
       <c r="P23" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q23" s="3">
         <v>1</v>
       </c>
       <c r="R23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S23" s="3" t="s">
+      <c r="T23" s="3">
+        <v>1</v>
+      </c>
+      <c r="U23" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T23" s="3">
-        <v>1</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -2611,52 +2611,52 @@
     <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>75</v>
-      </c>
       <c r="F24" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3">
         <v>4600</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q24" s="3">
         <v>30</v>
       </c>
       <c r="R24" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S24" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T24" s="3">
         <v>1</v>
       </c>
       <c r="U24" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -2679,56 +2679,56 @@
     <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3">
         <v>1.5</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q25" s="3">
         <v>30</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S25" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T25" s="3">
         <v>1</v>
       </c>
       <c r="U25" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -2751,56 +2751,56 @@
     <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="F26" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3">
         <v>3.1</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q26" s="3">
         <v>30</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S26" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T26" s="3">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -2823,52 +2823,52 @@
     <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="F27" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3">
         <v>170</v>
       </c>
       <c r="P27" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q27" s="3">
         <v>1</v>
       </c>
       <c r="R27" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S27" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S27" s="3" t="s">
+      <c r="T27" s="3">
+        <v>1</v>
+      </c>
+      <c r="U27" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T27" s="3">
-        <v>1</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -2891,52 +2891,52 @@
     <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C28" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E28" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>77</v>
-      </c>
       <c r="F28" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3">
         <v>4200</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q28" s="3">
         <v>30</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S28" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T28" s="3">
         <v>1</v>
       </c>
       <c r="U28" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -2959,52 +2959,52 @@
     <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E29" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="F29" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q29" s="3">
         <v>1</v>
       </c>
       <c r="R29" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S29" s="3" t="s">
+      <c r="T29" s="3">
+        <v>1</v>
+      </c>
+      <c r="U29" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T29" s="3">
-        <v>1</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -3016,10 +3016,10 @@
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AF29" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AG29" s="3"/>
       <c r="AH29" s="3"/>
@@ -3037,50 +3037,50 @@
     <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C30" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E30" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3">
         <v>0.24</v>
       </c>
       <c r="P30" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q30" s="3">
         <v>1</v>
       </c>
       <c r="R30" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S30" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S30" s="3" t="s">
+      <c r="T30" s="3">
+        <v>1</v>
+      </c>
+      <c r="U30" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T30" s="3">
-        <v>1</v>
-      </c>
-      <c r="U30" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -3103,50 +3103,50 @@
     <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E31" s="3" t="s">
         <v>82</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3">
         <v>0.47</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q31" s="3">
         <v>30</v>
       </c>
       <c r="R31" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S31" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T31" s="3">
         <v>1</v>
       </c>
       <c r="U31" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -3169,52 +3169,52 @@
     <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E32" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="F32" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q32" s="3">
         <v>1</v>
       </c>
       <c r="R32" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S32" s="3" t="s">
+      <c r="T32" s="3">
+        <v>1</v>
+      </c>
+      <c r="U32" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T32" s="3">
-        <v>1</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -3226,10 +3226,10 @@
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AF32" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG32" s="3"/>
       <c r="AH32" s="3"/>
@@ -3247,52 +3247,52 @@
     <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="F33" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q33" s="3">
         <v>30</v>
       </c>
       <c r="R33" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S33" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T33" s="3">
         <v>1</v>
       </c>
       <c r="U33" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3304,10 +3304,10 @@
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="AF33" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AG33" s="3"/>
       <c r="AH33" s="3"/>
@@ -3325,52 +3325,52 @@
     <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="F34" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3">
         <v>7400</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q34" s="3">
         <v>1</v>
       </c>
       <c r="R34" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S34" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="3" t="s">
+      <c r="T34" s="3">
+        <v>1</v>
+      </c>
+      <c r="U34" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T34" s="3">
-        <v>1</v>
-      </c>
-      <c r="U34" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -3393,52 +3393,52 @@
     <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="F35" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3">
         <v>26000</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q35" s="3">
         <v>30</v>
       </c>
       <c r="R35" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S35" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T35" s="3">
         <v>1</v>
       </c>
       <c r="U35" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3461,54 +3461,54 @@
     <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E36" s="3" t="s">
+      <c r="F36" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3">
         <v>22</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q36" s="3">
         <v>1</v>
       </c>
       <c r="R36" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S36" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S36" s="3" t="s">
+      <c r="T36" s="3">
+        <v>1</v>
+      </c>
+      <c r="U36" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T36" s="3">
-        <v>1</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3531,54 +3531,54 @@
     <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E37" s="3" t="s">
+      <c r="F37" s="3" t="s">
         <v>87</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>88</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3">
         <v>5.2</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
       </c>
       <c r="R37" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S37" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T37" s="3">
         <v>1</v>
       </c>
       <c r="U37" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
@@ -3601,52 +3601,52 @@
     <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="F38" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3">
         <v>4</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q38" s="3">
         <v>1</v>
       </c>
       <c r="R38" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S38" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S38" s="3" t="s">
+      <c r="T38" s="3">
+        <v>1</v>
+      </c>
+      <c r="U38" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T38" s="3">
-        <v>1</v>
-      </c>
-      <c r="U38" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
@@ -3669,52 +3669,52 @@
     <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="F39" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3">
         <v>400</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q39" s="3">
         <v>30</v>
       </c>
       <c r="R39" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S39" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T39" s="3">
         <v>1</v>
       </c>
       <c r="U39" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3737,50 +3737,50 @@
     <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E40" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3">
         <v>7000000</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q40" s="3">
         <v>1</v>
       </c>
       <c r="R40" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S40" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S40" s="3" t="s">
+      <c r="T40" s="3">
+        <v>1</v>
+      </c>
+      <c r="U40" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T40" s="3">
-        <v>1</v>
-      </c>
-      <c r="U40" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3803,52 +3803,52 @@
     <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3">
         <v>20000</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q41" s="3">
         <v>30</v>
       </c>
       <c r="R41" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S41" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T41" s="3">
         <v>1</v>
       </c>
       <c r="U41" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3871,52 +3871,52 @@
     <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="F42" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q42" s="3">
         <v>1</v>
       </c>
       <c r="R42" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S42" s="3" t="s">
+      <c r="T42" s="3">
+        <v>1</v>
+      </c>
+      <c r="U42" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T42" s="3">
-        <v>1</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -3928,10 +3928,10 @@
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
       <c r="AE42" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AF42" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AG42" s="3"/>
       <c r="AH42" s="3"/>
@@ -3943,52 +3943,52 @@
     <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E43" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="F43" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q43" s="3">
         <v>30</v>
       </c>
       <c r="R43" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S43" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T43" s="3">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
@@ -4000,10 +4000,10 @@
       <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
       <c r="AE43" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AF43" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AG43" s="3"/>
       <c r="AH43" s="3"/>
@@ -4015,50 +4015,50 @@
     <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E44" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>99</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3">
         <v>1000</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q44" s="3">
         <v>1</v>
       </c>
       <c r="R44" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S44" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S44" s="3" t="s">
+      <c r="T44" s="3">
+        <v>1</v>
+      </c>
+      <c r="U44" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T44" s="3">
-        <v>1</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -4081,52 +4081,52 @@
     <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3">
         <v>860000</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q45" s="3">
         <v>1</v>
       </c>
       <c r="R45" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S45" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S45" s="3" t="s">
+      <c r="T45" s="3">
+        <v>1</v>
+      </c>
+      <c r="U45" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T45" s="3">
-        <v>1</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -4149,52 +4149,52 @@
     <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>101</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3">
         <v>230000</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q46" s="3">
         <v>30</v>
       </c>
       <c r="R46" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S46" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T46" s="3">
         <v>1</v>
       </c>
       <c r="U46" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -4217,54 +4217,54 @@
     <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="F47" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3">
         <v>19</v>
       </c>
       <c r="P47" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q47" s="3">
         <v>1</v>
       </c>
       <c r="R47" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S47" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S47" s="3" t="s">
+      <c r="T47" s="3">
+        <v>1</v>
+      </c>
+      <c r="U47" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T47" s="3">
-        <v>1</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -4287,54 +4287,54 @@
     <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E48" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="F48" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3">
         <v>11</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q48" s="3">
         <v>30</v>
       </c>
       <c r="R48" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S48" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T48" s="3">
         <v>1</v>
       </c>
       <c r="U48" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -4357,52 +4357,52 @@
     <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C49" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E49" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3">
         <v>1000</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q49" s="3">
         <v>30</v>
       </c>
       <c r="R49" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S49" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T49" s="3">
         <v>1</v>
       </c>
       <c r="U49" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -4425,50 +4425,50 @@
     <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E50" s="3" t="s">
         <v>104</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3">
         <v>300</v>
       </c>
       <c r="P50" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q50" s="3">
         <v>1</v>
       </c>
       <c r="R50" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S50" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S50" s="3" t="s">
+      <c r="T50" s="3">
+        <v>1</v>
+      </c>
+      <c r="U50" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T50" s="3">
-        <v>1</v>
-      </c>
-      <c r="U50" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -4491,50 +4491,50 @@
     <row r="51" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E51" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3">
         <v>50</v>
       </c>
       <c r="P51" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q51" s="3">
         <v>1</v>
       </c>
       <c r="R51" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S51" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S51" s="3" t="s">
+      <c r="T51" s="3">
+        <v>1</v>
+      </c>
+      <c r="U51" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T51" s="3">
-        <v>1</v>
-      </c>
-      <c r="U51" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
@@ -4557,50 +4557,50 @@
     <row r="52" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E52" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3">
         <v>100</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q52" s="3">
         <v>30</v>
       </c>
       <c r="R52" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S52" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T52" s="3">
         <v>1</v>
       </c>
       <c r="U52" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
@@ -4623,50 +4623,50 @@
     <row r="53" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="3">
         <v>10000</v>
       </c>
       <c r="P53" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q53" s="3">
         <v>1</v>
       </c>
       <c r="R53" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S53" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S53" s="3" t="s">
+      <c r="T53" s="3">
+        <v>1</v>
+      </c>
+      <c r="U53" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T53" s="3">
-        <v>1</v>
-      </c>
-      <c r="U53" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
@@ -4689,52 +4689,52 @@
     <row r="54" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3">
         <v>250000</v>
       </c>
       <c r="P54" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q54" s="3">
         <v>1</v>
       </c>
       <c r="R54" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S54" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="S54" s="3" t="s">
+      <c r="T54" s="3">
+        <v>1</v>
+      </c>
+      <c r="U54" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="T54" s="3">
-        <v>1</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
@@ -4757,52 +4757,52 @@
     <row r="55" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E55" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3">
         <v>2</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q55" s="3">
         <v>30</v>
       </c>
       <c r="R55" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S55" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T55" s="3">
         <v>1</v>
       </c>
       <c r="U55" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
@@ -4825,54 +4825,54 @@
     <row r="56" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N56" s="3">
         <v>6.5</v>
       </c>
       <c r="O56" s="3"/>
       <c r="P56" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q56" s="3">
         <v>30</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T56" s="3">
         <v>1</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
@@ -4895,54 +4895,54 @@
     <row r="57" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N57" s="3">
         <v>5.5</v>
       </c>
       <c r="O57" s="3"/>
       <c r="P57" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q57" s="3">
         <v>30</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T57" s="3">
         <v>1</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
@@ -4965,54 +4965,54 @@
     <row r="58" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N58" s="3">
         <v>9.5</v>
       </c>
       <c r="O58" s="3"/>
       <c r="P58" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q58" s="3">
         <v>7</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T58" s="3">
         <v>1</v>
       </c>
       <c r="U58" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
@@ -5035,54 +5035,54 @@
     <row r="59" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N59" s="3">
         <v>6</v>
       </c>
       <c r="O59" s="3"/>
       <c r="P59" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q59" s="3">
         <v>7</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T59" s="3">
         <v>1</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
@@ -5105,54 +5105,54 @@
     <row r="60" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N60" s="3">
         <v>5</v>
       </c>
       <c r="O60" s="3"/>
       <c r="P60" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q60" s="3">
         <v>7</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="T60" s="3">
         <v>1</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
@@ -5175,54 +5175,54 @@
     <row r="61" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N61" s="3">
         <v>4</v>
       </c>
       <c r="O61" s="3"/>
       <c r="P61" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="Q61" s="3">
         <v>7</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="T61" s="3">
         <v>1</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
@@ -5245,54 +5245,54 @@
     <row r="62" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N62" s="3">
         <v>8</v>
       </c>
       <c r="O62" s="3"/>
       <c r="P62" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q62" s="3">
+        <v>1</v>
+      </c>
+      <c r="R62" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="T62" s="3">
+        <v>1</v>
+      </c>
+      <c r="U62" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>1</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S62" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="T62" s="3">
-        <v>1</v>
-      </c>
-      <c r="U62" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
@@ -5315,54 +5315,54 @@
     <row r="63" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N63" s="3">
         <v>5</v>
       </c>
       <c r="O63" s="3"/>
       <c r="P63" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>1</v>
+      </c>
+      <c r="R63" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S63" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="T63" s="3">
+        <v>1</v>
+      </c>
+      <c r="U63" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="Q63" s="3">
-        <v>1</v>
-      </c>
-      <c r="R63" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S63" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="T63" s="3">
-        <v>1</v>
-      </c>
-      <c r="U63" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3"/>
@@ -5385,54 +5385,54 @@
     <row r="64" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N64" s="3">
         <v>4</v>
       </c>
       <c r="O64" s="3"/>
       <c r="P64" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>1</v>
+      </c>
+      <c r="R64" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S64" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="T64" s="3">
+        <v>1</v>
+      </c>
+      <c r="U64" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="Q64" s="3">
-        <v>1</v>
-      </c>
-      <c r="R64" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S64" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="T64" s="3">
-        <v>1</v>
-      </c>
-      <c r="U64" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3"/>
@@ -5455,54 +5455,54 @@
     <row r="65" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K65" s="3"/>
       <c r="L65" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="N65" s="3">
         <v>3</v>
       </c>
       <c r="O65" s="3"/>
       <c r="P65" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>1</v>
+      </c>
+      <c r="R65" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="S65" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="T65" s="3">
+        <v>1</v>
+      </c>
+      <c r="U65" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="Q65" s="3">
-        <v>1</v>
-      </c>
-      <c r="R65" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="S65" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="T65" s="3">
-        <v>1</v>
-      </c>
-      <c r="U65" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -5525,52 +5525,52 @@
     <row r="66" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C66" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E66" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I66" s="3"/>
       <c r="J66" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K66" s="3"/>
       <c r="L66" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
       <c r="P66" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q66" s="3">
         <v>1</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T66" s="3">
         <v>1</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V66" s="3"/>
       <c r="W66" s="3"/>
@@ -5582,10 +5582,10 @@
       <c r="AC66" s="3"/>
       <c r="AD66" s="3"/>
       <c r="AE66" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AF66" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG66" s="3"/>
       <c r="AH66" s="3"/>
@@ -5609,52 +5609,52 @@
     <row r="67" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E67" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E67" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I67" s="3"/>
       <c r="J67" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K67" s="3"/>
       <c r="L67" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q67" s="3">
         <v>1</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T67" s="3">
         <v>1</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
@@ -5666,10 +5666,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AF67" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
@@ -5693,52 +5693,52 @@
     <row r="68" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E68" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N68" s="3"/>
       <c r="O68" s="3"/>
       <c r="P68" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q68" s="3">
         <v>30</v>
       </c>
       <c r="R68" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S68" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T68" s="3">
         <v>1</v>
       </c>
       <c r="U68" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
@@ -5750,10 +5750,10 @@
       <c r="AC68" s="3"/>
       <c r="AD68" s="3"/>
       <c r="AE68" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF68" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="AF68" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="AG68" s="3"/>
       <c r="AH68" s="3"/>
@@ -5765,52 +5765,52 @@
     <row r="69" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="E69" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E69" s="3" t="s">
-        <v>122</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N69" s="3"/>
       <c r="O69" s="3"/>
       <c r="P69" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q69" s="3">
         <v>30</v>
       </c>
       <c r="R69" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S69" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T69" s="3">
         <v>1</v>
       </c>
       <c r="U69" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
@@ -5822,10 +5822,10 @@
       <c r="AC69" s="3"/>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AF69" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="AG69" s="3"/>
       <c r="AH69" s="3"/>

--- a/inst/extdata/northern_cheyenne_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/northern_cheyenne_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kwong01\TADACommunityHub\inst\extdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67033712-198A-4757-B500-AE2A7181765C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{67033712-198A-4757-B500-AE2A7181765C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{485F0FB6-F39B-4C36-9213-59E490224E28}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="10320" xr2:uid="{E55A9BC7-10AB-4EF2-8E95-202746609CFA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E55A9BC7-10AB-4EF2-8E95-202746609CFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="158">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -143,12 +143,6 @@
     <t>hardness_param_4</t>
   </si>
   <si>
-    <t>hardness_param_5</t>
-  </si>
-  <si>
-    <t>hardness_param_6</t>
-  </si>
-  <si>
     <t>pH_param_1</t>
   </si>
   <si>
@@ -323,12 +317,6 @@
     <t>ALUMINUM</t>
   </si>
   <si>
-    <t>EPA Aluminum calculator</t>
-  </si>
-  <si>
-    <t>Additional Information</t>
-  </si>
-  <si>
     <t>Barium</t>
   </si>
   <si>
@@ -434,9 +422,6 @@
     <t>Early life stages absent</t>
   </si>
   <si>
-    <t>((0.0577/(1+10^(7.688-pH))) + (2.487/(1+10^(pH-7.688)))) * 1.45*10^(0.028*(25-Temperature))</t>
-  </si>
-  <si>
     <t>CHROMIUM, TRIVALENT, TOTAL</t>
   </si>
   <si>
@@ -485,7 +470,46 @@
     <t>0.986*e^(0.8473*(ln(hardness))+0.884)</t>
   </si>
   <si>
-    <t>EquationFormula</t>
+    <t>pHThreshold</t>
+  </si>
+  <si>
+    <t>pHDirection</t>
+  </si>
+  <si>
+    <t>TemperatureExtreme</t>
+  </si>
+  <si>
+    <t>MinEqMagnitude</t>
+  </si>
+  <si>
+    <t>MaxEqMagnitude</t>
+  </si>
+  <si>
+    <t>pH_param_5</t>
+  </si>
+  <si>
+    <t>pH_param_6</t>
+  </si>
+  <si>
+    <t>pH_param_7</t>
+  </si>
+  <si>
+    <t>pH_param_8</t>
+  </si>
+  <si>
+    <t>pH_param_9</t>
+  </si>
+  <si>
+    <t>((0.0577/(1+10^(7.688-pH))) + (2.487/(1+10^(pH-7.688)))) * 1.45*10^(0.028*(25-max(Temperature,7)))</t>
+  </si>
+  <si>
+    <t>Min</t>
+  </si>
+  <si>
+    <t>Max</t>
+  </si>
+  <si>
+    <t>Equation</t>
   </si>
 </sst>
 </file>
@@ -891,16 +915,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88090834-75EE-4F17-A178-5F0CE015882D}">
-  <dimension ref="A1:AP69"/>
+  <dimension ref="A1:AX69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="9.140625" style="5"/>
     <col min="3" max="3" width="24.7109375" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5703125" style="5" customWidth="1"/>
-    <col min="5" max="16384" width="9.140625" style="5"/>
+    <col min="5" max="31" width="9.140625" style="5"/>
+    <col min="32" max="32" width="102.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="19.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="8.85546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" ht="47.25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -995,86 +1025,110 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AK1" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AG1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AH1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AJ1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AK1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AL1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AS1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3">
         <v>5.6</v>
       </c>
       <c r="P2" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q2" s="3">
-        <v>1</v>
-      </c>
-      <c r="R2" s="3" t="s">
+      <c r="T2" s="3">
+        <v>1</v>
+      </c>
+      <c r="U2" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T2" s="3">
-        <v>1</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
@@ -1093,54 +1147,55 @@
       <c r="AJ2" s="3"/>
       <c r="AK2" s="3"/>
       <c r="AL2" s="3"/>
-    </row>
-    <row r="3" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM2" s="3"/>
+    </row>
+    <row r="3" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3">
         <v>640</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q3" s="3">
         <v>30</v>
       </c>
       <c r="R3" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T3" s="3">
+        <v>1</v>
+      </c>
+      <c r="U3" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T3" s="3">
-        <v>1</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
@@ -1159,58 +1214,59 @@
       <c r="AJ3" s="3"/>
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
-    </row>
-    <row r="4" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM3" s="3"/>
+    </row>
+    <row r="4" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3">
         <v>340</v>
       </c>
       <c r="P4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q4" s="3">
-        <v>1</v>
-      </c>
-      <c r="R4" s="3" t="s">
+      <c r="T4" s="3">
+        <v>1</v>
+      </c>
+      <c r="U4" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T4" s="3">
-        <v>1</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
@@ -1229,58 +1285,59 @@
       <c r="AJ4" s="3"/>
       <c r="AK4" s="3"/>
       <c r="AL4" s="3"/>
-    </row>
-    <row r="5" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM4" s="3"/>
+    </row>
+    <row r="5" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3">
         <v>150</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q5" s="3">
         <v>30</v>
       </c>
       <c r="R5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T5" s="3">
+        <v>1</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T5" s="3">
-        <v>1</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
@@ -1299,56 +1356,57 @@
       <c r="AJ5" s="3"/>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
-    </row>
-    <row r="6" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM5" s="3"/>
+    </row>
+    <row r="6" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="P6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>1</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q6" s="3">
-        <v>1</v>
-      </c>
-      <c r="R6" s="3" t="s">
+      <c r="T6" s="3">
+        <v>1</v>
+      </c>
+      <c r="U6" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T6" s="3">
-        <v>1</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
@@ -1367,56 +1425,57 @@
       <c r="AJ6" s="3"/>
       <c r="AK6" s="3"/>
       <c r="AL6" s="3"/>
-    </row>
-    <row r="7" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM6" s="3"/>
+    </row>
+    <row r="7" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3">
         <v>0.14000000000000001</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q7" s="3">
         <v>30</v>
       </c>
       <c r="R7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T7" s="3">
+        <v>1</v>
+      </c>
+      <c r="U7" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T7" s="3">
-        <v>1</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
@@ -1435,56 +1494,57 @@
       <c r="AJ7" s="3"/>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
-    </row>
-    <row r="8" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM7" s="3"/>
+    </row>
+    <row r="8" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>57</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>59</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>1</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q8" s="3">
-        <v>1</v>
-      </c>
-      <c r="R8" s="3" t="s">
+      <c r="T8" s="3">
+        <v>1</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -1496,77 +1556,75 @@
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="AG8" s="3">
+        <v>134</v>
+      </c>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="3"/>
+      <c r="AI8" s="3">
         <v>1.1366719999999999</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AJ8" s="3">
         <v>4.1838E-2</v>
       </c>
-      <c r="AI8" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>0.97889999999999999</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>-3.8660000000000001</v>
       </c>
-      <c r="AL8" s="3"/>
-    </row>
-    <row r="9" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>1</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q9" s="3">
-        <v>1</v>
-      </c>
-      <c r="R9" s="3" t="s">
+      <c r="T9" s="3">
+        <v>1</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -1578,73 +1636,73 @@
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
-      <c r="AI9" s="3">
+      <c r="AI9" s="3"/>
+      <c r="AJ9" s="3">
         <v>0.316</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>0.81899999999999995</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>3.7256</v>
       </c>
-      <c r="AL9" s="3"/>
-    </row>
-    <row r="10" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q10" s="3">
         <v>30</v>
       </c>
       <c r="R10" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T10" s="3">
+        <v>1</v>
+      </c>
+      <c r="U10" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -1656,75 +1714,75 @@
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AF10" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
-      <c r="AI10" s="3">
+      <c r="AI10" s="3"/>
+      <c r="AJ10" s="3">
         <v>0.86</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>0.81899999999999995</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>0.68479999999999996</v>
       </c>
-      <c r="AL10" s="3"/>
-    </row>
-    <row r="11" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3">
         <v>16</v>
       </c>
       <c r="P11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q11" s="3">
-        <v>1</v>
-      </c>
-      <c r="R11" s="3" t="s">
+      <c r="T11" s="3">
+        <v>1</v>
+      </c>
+      <c r="U11" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T11" s="3">
-        <v>1</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -1743,58 +1801,59 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
-    </row>
-    <row r="12" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM11" s="3"/>
+    </row>
+    <row r="12" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3">
         <v>11</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q12" s="3">
         <v>30</v>
       </c>
       <c r="R12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T12" s="3">
+        <v>1</v>
+      </c>
+      <c r="U12" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T12" s="3">
-        <v>1</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
@@ -1813,56 +1872,57 @@
       <c r="AJ12" s="3"/>
       <c r="AK12" s="3"/>
       <c r="AL12" s="3"/>
-    </row>
-    <row r="13" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM12" s="3"/>
+    </row>
+    <row r="13" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3">
         <v>1300</v>
       </c>
       <c r="P13" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>1</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q13" s="3">
-        <v>1</v>
-      </c>
-      <c r="R13" s="3" t="s">
+      <c r="T13" s="3">
+        <v>1</v>
+      </c>
+      <c r="U13" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T13" s="3">
-        <v>1</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
@@ -1881,56 +1941,57 @@
       <c r="AJ13" s="3"/>
       <c r="AK13" s="3"/>
       <c r="AL13" s="3"/>
-    </row>
-    <row r="14" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM13" s="3"/>
+    </row>
+    <row r="14" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>1</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q14" s="3">
-        <v>1</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="T14" s="3">
+        <v>1</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T14" s="3">
-        <v>1</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
@@ -1942,77 +2003,75 @@
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AF14" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="AG14" s="3">
+        <v>137</v>
+      </c>
+      <c r="AG14" s="3"/>
+      <c r="AH14" s="3"/>
+      <c r="AI14" s="3">
         <v>1.4620299999999999</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AJ14" s="3">
         <v>0.14571200000000001</v>
       </c>
-      <c r="AI14" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>1.2729999999999999</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>-1.46</v>
       </c>
-      <c r="AL14" s="3"/>
-    </row>
-    <row r="15" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q15" s="3">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T15" s="3">
+        <v>1</v>
+      </c>
+      <c r="U15" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T15" s="3">
-        <v>1</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
@@ -2024,79 +2083,77 @@
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="AG15" s="3">
+        <v>138</v>
+      </c>
+      <c r="AG15" s="3"/>
+      <c r="AH15" s="3"/>
+      <c r="AI15" s="3">
         <v>1.4620299999999999</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AJ15" s="3">
         <v>0.14571200000000001</v>
       </c>
-      <c r="AI15" s="3">
-        <v>1</v>
-      </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>1.2729999999999999</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-4.7050000000000001</v>
       </c>
-      <c r="AL15" s="3"/>
-    </row>
-    <row r="16" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3">
         <v>1.4</v>
       </c>
       <c r="P16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>1</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q16" s="3">
-        <v>1</v>
-      </c>
-      <c r="R16" s="3" t="s">
+      <c r="T16" s="3">
+        <v>1</v>
+      </c>
+      <c r="U16" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T16" s="3">
-        <v>1</v>
-      </c>
-      <c r="U16" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
@@ -2115,56 +2172,57 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
-    </row>
-    <row r="17" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM16" s="3"/>
+    </row>
+    <row r="17" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3">
         <v>0.05</v>
       </c>
       <c r="P17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>1</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S17" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q17" s="3">
-        <v>1</v>
-      </c>
-      <c r="R17" s="3" t="s">
+      <c r="T17" s="3">
+        <v>1</v>
+      </c>
+      <c r="U17" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
@@ -2183,56 +2241,57 @@
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
-    </row>
-    <row r="18" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM17" s="3"/>
+    </row>
+    <row r="18" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3">
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q18" s="3">
         <v>30</v>
       </c>
       <c r="R18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T18" s="3">
+        <v>1</v>
+      </c>
+      <c r="U18" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T18" s="3">
-        <v>1</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2251,54 +2310,55 @@
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
-    </row>
-    <row r="19" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM18" s="3"/>
+    </row>
+    <row r="19" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3">
         <v>0.3</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q19" s="3">
         <v>30</v>
       </c>
       <c r="R19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T19" s="3">
+        <v>1</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T19" s="3">
-        <v>1</v>
-      </c>
-      <c r="U19" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2317,54 +2377,55 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
-    </row>
-    <row r="20" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM19" s="3"/>
+    </row>
+    <row r="20" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3">
         <v>0.3</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="Q20" s="3">
         <v>30</v>
       </c>
       <c r="R20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T20" s="3">
+        <v>1</v>
+      </c>
+      <c r="U20" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T20" s="3">
-        <v>1</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2383,56 +2444,57 @@
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
-    </row>
-    <row r="21" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM20" s="3"/>
+    </row>
+    <row r="21" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>1</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S21" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q21" s="3">
-        <v>1</v>
-      </c>
-      <c r="R21" s="3" t="s">
+      <c r="T21" s="3">
+        <v>1</v>
+      </c>
+      <c r="U21" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T21" s="3">
-        <v>1</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2444,73 +2506,73 @@
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AF21" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="AG21" s="3"/>
       <c r="AH21" s="3"/>
-      <c r="AI21" s="3">
+      <c r="AI21" s="3"/>
+      <c r="AJ21" s="3">
         <v>0.998</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>0.84599999999999997</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2.2549999999999999</v>
       </c>
-      <c r="AL21" s="3"/>
-    </row>
-    <row r="22" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q22" s="3">
         <v>30</v>
       </c>
       <c r="R22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T22" s="3">
+        <v>1</v>
+      </c>
+      <c r="U22" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T22" s="3">
-        <v>1</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2522,73 +2584,73 @@
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AF22" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="AG22" s="3"/>
       <c r="AH22" s="3"/>
-      <c r="AI22" s="3">
+      <c r="AI22" s="3"/>
+      <c r="AJ22" s="3">
         <v>0.997</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>0.84599999999999997</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>5.8400000000000001E-2</v>
       </c>
-      <c r="AL22" s="3"/>
-    </row>
-    <row r="23" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3">
         <v>610</v>
       </c>
       <c r="P23" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>1</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q23" s="3">
-        <v>1</v>
-      </c>
-      <c r="R23" s="3" t="s">
+      <c r="T23" s="3">
+        <v>1</v>
+      </c>
+      <c r="U23" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T23" s="3">
-        <v>1</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -2607,56 +2669,57 @@
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
-    </row>
-    <row r="24" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM23" s="3"/>
+    </row>
+    <row r="24" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3">
         <v>4600</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q24" s="3">
         <v>30</v>
       </c>
       <c r="R24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T24" s="3">
+        <v>1</v>
+      </c>
+      <c r="U24" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T24" s="3">
-        <v>1</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -2675,60 +2738,61 @@
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
-    </row>
-    <row r="25" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM24" s="3"/>
+    </row>
+    <row r="25" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3">
         <v>1.5</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q25" s="3">
         <v>30</v>
       </c>
       <c r="R25" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T25" s="3">
+        <v>1</v>
+      </c>
+      <c r="U25" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T25" s="3">
-        <v>1</v>
-      </c>
-      <c r="U25" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -2747,60 +2811,61 @@
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
-    </row>
-    <row r="26" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM25" s="3"/>
+    </row>
+    <row r="26" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3">
         <v>3.1</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q26" s="3">
         <v>30</v>
       </c>
       <c r="R26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T26" s="3">
+        <v>1</v>
+      </c>
+      <c r="U26" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T26" s="3">
-        <v>1</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -2819,56 +2884,57 @@
       <c r="AJ26" s="3"/>
       <c r="AK26" s="3"/>
       <c r="AL26" s="3"/>
-    </row>
-    <row r="27" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM26" s="3"/>
+    </row>
+    <row r="27" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3">
         <v>170</v>
       </c>
       <c r="P27" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>1</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S27" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q27" s="3">
-        <v>1</v>
-      </c>
-      <c r="R27" s="3" t="s">
+      <c r="T27" s="3">
+        <v>1</v>
+      </c>
+      <c r="U27" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T27" s="3">
-        <v>1</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
@@ -2887,56 +2953,57 @@
       <c r="AJ27" s="3"/>
       <c r="AK27" s="3"/>
       <c r="AL27" s="3"/>
-    </row>
-    <row r="28" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM27" s="3"/>
+    </row>
+    <row r="28" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3">
         <v>4200</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q28" s="3">
         <v>30</v>
       </c>
       <c r="R28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T28" s="3">
+        <v>1</v>
+      </c>
+      <c r="U28" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T28" s="3">
-        <v>1</v>
-      </c>
-      <c r="U28" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -2955,56 +3022,57 @@
       <c r="AJ28" s="3"/>
       <c r="AK28" s="3"/>
       <c r="AL28" s="3"/>
-    </row>
-    <row r="29" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM28" s="3"/>
+    </row>
+    <row r="29" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>1</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q29" s="3">
-        <v>1</v>
-      </c>
-      <c r="R29" s="3" t="s">
+      <c r="T29" s="3">
+        <v>1</v>
+      </c>
+      <c r="U29" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T29" s="3">
-        <v>1</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
@@ -3016,71 +3084,71 @@
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AF29" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="AG29" s="3"/>
       <c r="AH29" s="3"/>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3"/>
+      <c r="AJ29" s="3">
         <v>0.85</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>1.72</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-6.59</v>
       </c>
-      <c r="AL29" s="3"/>
-    </row>
-    <row r="30" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3">
         <v>0.24</v>
       </c>
       <c r="P30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>1</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S30" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q30" s="3">
-        <v>1</v>
-      </c>
-      <c r="R30" s="3" t="s">
+      <c r="T30" s="3">
+        <v>1</v>
+      </c>
+      <c r="U30" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S30" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T30" s="3">
-        <v>1</v>
-      </c>
-      <c r="U30" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -3100,53 +3168,53 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
     </row>
-    <row r="31" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3">
         <v>0.47</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q31" s="3">
         <v>30</v>
       </c>
       <c r="R31" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T31" s="3">
+        <v>1</v>
+      </c>
+      <c r="U31" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T31" s="3">
-        <v>1</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
@@ -3166,55 +3234,55 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
     </row>
-    <row r="32" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>1</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q32" s="3">
-        <v>1</v>
-      </c>
-      <c r="R32" s="3" t="s">
+      <c r="T32" s="3">
+        <v>1</v>
+      </c>
+      <c r="U32" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T32" s="3">
-        <v>1</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
@@ -3226,73 +3294,73 @@
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AF32" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="AG32" s="3"/>
       <c r="AH32" s="3"/>
-      <c r="AI32" s="3">
+      <c r="AI32" s="3"/>
+      <c r="AJ32" s="3">
         <v>0.97799999999999998</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>0.84730000000000005</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>0.88400000000000001</v>
       </c>
-      <c r="AL32" s="3"/>
-    </row>
-    <row r="33" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q33" s="3">
         <v>30</v>
       </c>
       <c r="R33" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T33" s="3">
+        <v>1</v>
+      </c>
+      <c r="U33" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T33" s="3">
-        <v>1</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3304,73 +3372,73 @@
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AF33" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="AG33" s="3"/>
       <c r="AH33" s="3"/>
-      <c r="AI33" s="3">
+      <c r="AI33" s="3"/>
+      <c r="AJ33" s="3">
         <v>0.98599999999999999</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>0.84730000000000005</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>0.88400000000000001</v>
       </c>
-      <c r="AL33" s="3"/>
-    </row>
-    <row r="34" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3">
         <v>7400</v>
       </c>
       <c r="P34" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>1</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S34" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q34" s="3">
-        <v>1</v>
-      </c>
-      <c r="R34" s="3" t="s">
+      <c r="T34" s="3">
+        <v>1</v>
+      </c>
+      <c r="U34" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T34" s="3">
-        <v>1</v>
-      </c>
-      <c r="U34" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
@@ -3389,56 +3457,57 @@
       <c r="AJ34" s="3"/>
       <c r="AK34" s="3"/>
       <c r="AL34" s="3"/>
-    </row>
-    <row r="35" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM34" s="3"/>
+    </row>
+    <row r="35" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3">
         <v>26000</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q35" s="3">
         <v>30</v>
       </c>
       <c r="R35" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T35" s="3">
+        <v>1</v>
+      </c>
+      <c r="U35" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T35" s="3">
-        <v>1</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3457,58 +3526,59 @@
       <c r="AJ35" s="3"/>
       <c r="AK35" s="3"/>
       <c r="AL35" s="3"/>
-    </row>
-    <row r="36" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM35" s="3"/>
+    </row>
+    <row r="36" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3">
         <v>22</v>
       </c>
       <c r="P36" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>1</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S36" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q36" s="3">
-        <v>1</v>
-      </c>
-      <c r="R36" s="3" t="s">
+      <c r="T36" s="3">
+        <v>1</v>
+      </c>
+      <c r="U36" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S36" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T36" s="3">
-        <v>1</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
@@ -3527,58 +3597,59 @@
       <c r="AJ36" s="3"/>
       <c r="AK36" s="3"/>
       <c r="AL36" s="3"/>
-    </row>
-    <row r="37" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM36" s="3"/>
+    </row>
+    <row r="37" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>87</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3">
         <v>5.2</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
       </c>
       <c r="R37" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T37" s="3">
+        <v>1</v>
+      </c>
+      <c r="U37" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S37" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T37" s="3">
-        <v>1</v>
-      </c>
-      <c r="U37" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
@@ -3597,56 +3668,57 @@
       <c r="AJ37" s="3"/>
       <c r="AK37" s="3"/>
       <c r="AL37" s="3"/>
-    </row>
-    <row r="38" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM37" s="3"/>
+    </row>
+    <row r="38" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3">
         <v>4</v>
       </c>
       <c r="P38" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>1</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S38" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q38" s="3">
-        <v>1</v>
-      </c>
-      <c r="R38" s="3" t="s">
+      <c r="T38" s="3">
+        <v>1</v>
+      </c>
+      <c r="U38" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T38" s="3">
-        <v>1</v>
-      </c>
-      <c r="U38" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
@@ -3665,56 +3737,57 @@
       <c r="AJ38" s="3"/>
       <c r="AK38" s="3"/>
       <c r="AL38" s="3"/>
-    </row>
-    <row r="39" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM38" s="3"/>
+    </row>
+    <row r="39" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3">
         <v>400</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q39" s="3">
         <v>30</v>
       </c>
       <c r="R39" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S39" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T39" s="3">
+        <v>1</v>
+      </c>
+      <c r="U39" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S39" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T39" s="3">
-        <v>1</v>
-      </c>
-      <c r="U39" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
@@ -3733,54 +3806,55 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
-    </row>
-    <row r="40" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM39" s="3"/>
+    </row>
+    <row r="40" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3">
         <v>7000000</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="Q40" s="3">
         <v>1</v>
       </c>
       <c r="R40" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T40" s="3">
+        <v>1</v>
+      </c>
+      <c r="U40" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T40" s="3">
-        <v>1</v>
-      </c>
-      <c r="U40" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
@@ -3799,56 +3873,57 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
-    </row>
-    <row r="41" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM40" s="3"/>
+    </row>
+    <row r="41" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3">
         <v>20000</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q41" s="3">
         <v>30</v>
       </c>
       <c r="R41" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T41" s="3">
+        <v>1</v>
+      </c>
+      <c r="U41" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T41" s="3">
-        <v>1</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3867,56 +3942,57 @@
       <c r="AJ41" s="3"/>
       <c r="AK41" s="3"/>
       <c r="AL41" s="3"/>
-    </row>
-    <row r="42" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM41" s="3"/>
+    </row>
+    <row r="42" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D42" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>1</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q42" s="3">
-        <v>1</v>
-      </c>
-      <c r="R42" s="3" t="s">
+      <c r="T42" s="3">
+        <v>1</v>
+      </c>
+      <c r="U42" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T42" s="3">
-        <v>1</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
@@ -3927,68 +4003,65 @@
       <c r="AB42" s="3"/>
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
-      <c r="AE42" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF42" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="AE42" s="3"/>
+      <c r="AF42" s="3"/>
       <c r="AG42" s="3"/>
       <c r="AH42" s="3"/>
       <c r="AI42" s="3"/>
       <c r="AJ42" s="3"/>
       <c r="AK42" s="3"/>
       <c r="AL42" s="3"/>
-    </row>
-    <row r="43" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM42" s="3"/>
+    </row>
+    <row r="43" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D43" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q43" s="3">
         <v>30</v>
       </c>
       <c r="R43" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T43" s="3">
+        <v>1</v>
+      </c>
+      <c r="U43" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T43" s="3">
-        <v>1</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
@@ -3999,66 +4072,63 @@
       <c r="AB43" s="3"/>
       <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
-      <c r="AE43" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="AF43" s="3" t="s">
-        <v>95</v>
-      </c>
+      <c r="AE43" s="3"/>
+      <c r="AF43" s="3"/>
       <c r="AG43" s="3"/>
       <c r="AH43" s="3"/>
       <c r="AI43" s="3"/>
       <c r="AJ43" s="3"/>
       <c r="AK43" s="3"/>
       <c r="AL43" s="3"/>
-    </row>
-    <row r="44" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM43" s="3"/>
+    </row>
+    <row r="44" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3">
         <v>1000</v>
       </c>
       <c r="P44" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>1</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q44" s="3">
-        <v>1</v>
-      </c>
-      <c r="R44" s="3" t="s">
+      <c r="T44" s="3">
+        <v>1</v>
+      </c>
+      <c r="U44" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T44" s="3">
-        <v>1</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
@@ -4077,56 +4147,57 @@
       <c r="AJ44" s="3"/>
       <c r="AK44" s="3"/>
       <c r="AL44" s="3"/>
-    </row>
-    <row r="45" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM44" s="3"/>
+    </row>
+    <row r="45" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3">
         <v>860000</v>
       </c>
       <c r="P45" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>1</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S45" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q45" s="3">
-        <v>1</v>
-      </c>
-      <c r="R45" s="3" t="s">
+      <c r="T45" s="3">
+        <v>1</v>
+      </c>
+      <c r="U45" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T45" s="3">
-        <v>1</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -4145,56 +4216,57 @@
       <c r="AJ45" s="3"/>
       <c r="AK45" s="3"/>
       <c r="AL45" s="3"/>
-    </row>
-    <row r="46" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM45" s="3"/>
+    </row>
+    <row r="46" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3">
         <v>230000</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q46" s="3">
         <v>30</v>
       </c>
       <c r="R46" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T46" s="3">
+        <v>1</v>
+      </c>
+      <c r="U46" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T46" s="3">
-        <v>1</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -4213,58 +4285,59 @@
       <c r="AJ46" s="3"/>
       <c r="AK46" s="3"/>
       <c r="AL46" s="3"/>
-    </row>
-    <row r="47" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM46" s="3"/>
+    </row>
+    <row r="47" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D47" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3">
         <v>19</v>
       </c>
       <c r="P47" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>1</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S47" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q47" s="3">
-        <v>1</v>
-      </c>
-      <c r="R47" s="3" t="s">
+      <c r="T47" s="3">
+        <v>1</v>
+      </c>
+      <c r="U47" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T47" s="3">
-        <v>1</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -4283,58 +4356,59 @@
       <c r="AJ47" s="3"/>
       <c r="AK47" s="3"/>
       <c r="AL47" s="3"/>
-    </row>
-    <row r="48" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM47" s="3"/>
+    </row>
+    <row r="48" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D48" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>54</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3">
         <v>11</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q48" s="3">
         <v>30</v>
       </c>
       <c r="R48" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T48" s="3">
+        <v>1</v>
+      </c>
+      <c r="U48" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T48" s="3">
-        <v>1</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -4353,56 +4427,57 @@
       <c r="AJ48" s="3"/>
       <c r="AK48" s="3"/>
       <c r="AL48" s="3"/>
-    </row>
-    <row r="49" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM48" s="3"/>
+    </row>
+    <row r="49" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3">
         <v>1000</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q49" s="3">
         <v>30</v>
       </c>
       <c r="R49" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T49" s="3">
+        <v>1</v>
+      </c>
+      <c r="U49" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -4421,54 +4496,55 @@
       <c r="AJ49" s="3"/>
       <c r="AK49" s="3"/>
       <c r="AL49" s="3"/>
-    </row>
-    <row r="50" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM49" s="3"/>
+    </row>
+    <row r="50" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3">
         <v>300</v>
       </c>
       <c r="P50" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>1</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S50" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q50" s="3">
-        <v>1</v>
-      </c>
-      <c r="R50" s="3" t="s">
+      <c r="T50" s="3">
+        <v>1</v>
+      </c>
+      <c r="U50" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S50" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T50" s="3">
-        <v>1</v>
-      </c>
-      <c r="U50" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -4487,54 +4563,55 @@
       <c r="AJ50" s="3"/>
       <c r="AK50" s="3"/>
       <c r="AL50" s="3"/>
-    </row>
-    <row r="51" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM50" s="3"/>
+    </row>
+    <row r="51" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3">
         <v>50</v>
       </c>
       <c r="P51" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>1</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S51" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q51" s="3">
-        <v>1</v>
-      </c>
-      <c r="R51" s="3" t="s">
+      <c r="T51" s="3">
+        <v>1</v>
+      </c>
+      <c r="U51" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S51" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T51" s="3">
-        <v>1</v>
-      </c>
-      <c r="U51" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
@@ -4553,54 +4630,55 @@
       <c r="AJ51" s="3"/>
       <c r="AK51" s="3"/>
       <c r="AL51" s="3"/>
-    </row>
-    <row r="52" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM51" s="3"/>
+    </row>
+    <row r="52" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3">
         <v>100</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q52" s="3">
         <v>30</v>
       </c>
       <c r="R52" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T52" s="3">
+        <v>1</v>
+      </c>
+      <c r="U52" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T52" s="3">
-        <v>1</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
@@ -4619,54 +4697,55 @@
       <c r="AJ52" s="3"/>
       <c r="AK52" s="3"/>
       <c r="AL52" s="3"/>
-    </row>
-    <row r="53" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM52" s="3"/>
+    </row>
+    <row r="53" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="3">
         <v>10000</v>
       </c>
       <c r="P53" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>1</v>
+      </c>
+      <c r="R53" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S53" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q53" s="3">
-        <v>1</v>
-      </c>
-      <c r="R53" s="3" t="s">
+      <c r="T53" s="3">
+        <v>1</v>
+      </c>
+      <c r="U53" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S53" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T53" s="3">
-        <v>1</v>
-      </c>
-      <c r="U53" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
@@ -4685,56 +4764,57 @@
       <c r="AJ53" s="3"/>
       <c r="AK53" s="3"/>
       <c r="AL53" s="3"/>
-    </row>
-    <row r="54" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM53" s="3"/>
+    </row>
+    <row r="54" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3">
         <v>250000</v>
       </c>
       <c r="P54" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>1</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S54" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Q54" s="3">
-        <v>1</v>
-      </c>
-      <c r="R54" s="3" t="s">
+      <c r="T54" s="3">
+        <v>1</v>
+      </c>
+      <c r="U54" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T54" s="3">
-        <v>1</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
@@ -4753,56 +4833,57 @@
       <c r="AJ54" s="3"/>
       <c r="AK54" s="3"/>
       <c r="AL54" s="3"/>
-    </row>
-    <row r="55" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM54" s="3"/>
+    </row>
+    <row r="55" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3">
         <v>2</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q55" s="3">
         <v>30</v>
       </c>
       <c r="R55" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S55" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T55" s="3">
+        <v>1</v>
+      </c>
+      <c r="U55" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S55" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T55" s="3">
-        <v>1</v>
-      </c>
-      <c r="U55" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
@@ -4821,58 +4902,59 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
-    </row>
-    <row r="56" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM55" s="3"/>
+    </row>
+    <row r="56" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N56" s="3">
         <v>6.5</v>
       </c>
       <c r="O56" s="3"/>
       <c r="P56" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Q56" s="3">
         <v>30</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T56" s="3">
         <v>1</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
@@ -4891,58 +4973,59 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
-    </row>
-    <row r="57" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM56" s="3"/>
+    </row>
+    <row r="57" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N57" s="3">
         <v>5.5</v>
       </c>
       <c r="O57" s="3"/>
       <c r="P57" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Q57" s="3">
         <v>30</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T57" s="3">
         <v>1</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
@@ -4961,58 +5044,59 @@
       <c r="AJ57" s="3"/>
       <c r="AK57" s="3"/>
       <c r="AL57" s="3"/>
-    </row>
-    <row r="58" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM57" s="3"/>
+    </row>
+    <row r="58" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N58" s="3">
         <v>9.5</v>
       </c>
       <c r="O58" s="3"/>
       <c r="P58" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Q58" s="3">
         <v>7</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T58" s="3">
         <v>1</v>
       </c>
       <c r="U58" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
@@ -5031,58 +5115,59 @@
       <c r="AJ58" s="3"/>
       <c r="AK58" s="3"/>
       <c r="AL58" s="3"/>
-    </row>
-    <row r="59" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM58" s="3"/>
+    </row>
+    <row r="59" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N59" s="3">
         <v>6</v>
       </c>
       <c r="O59" s="3"/>
       <c r="P59" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Q59" s="3">
         <v>7</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T59" s="3">
         <v>1</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
@@ -5101,58 +5186,59 @@
       <c r="AJ59" s="3"/>
       <c r="AK59" s="3"/>
       <c r="AL59" s="3"/>
-    </row>
-    <row r="60" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM59" s="3"/>
+    </row>
+    <row r="60" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N60" s="3">
         <v>5</v>
       </c>
       <c r="O60" s="3"/>
       <c r="P60" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Q60" s="3">
         <v>7</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="T60" s="3">
         <v>1</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
@@ -5171,58 +5257,59 @@
       <c r="AJ60" s="3"/>
       <c r="AK60" s="3"/>
       <c r="AL60" s="3"/>
-    </row>
-    <row r="61" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM60" s="3"/>
+    </row>
+    <row r="61" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N61" s="3">
         <v>4</v>
       </c>
       <c r="O61" s="3"/>
       <c r="P61" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Q61" s="3">
         <v>7</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="T61" s="3">
         <v>1</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
@@ -5241,58 +5328,59 @@
       <c r="AJ61" s="3"/>
       <c r="AK61" s="3"/>
       <c r="AL61" s="3"/>
-    </row>
-    <row r="62" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM61" s="3"/>
+    </row>
+    <row r="62" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N62" s="3">
         <v>8</v>
       </c>
       <c r="O62" s="3"/>
       <c r="P62" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Q62" s="3">
         <v>1</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="T62" s="3">
         <v>1</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
@@ -5311,58 +5399,59 @@
       <c r="AJ62" s="3"/>
       <c r="AK62" s="3"/>
       <c r="AL62" s="3"/>
-    </row>
-    <row r="63" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM62" s="3"/>
+    </row>
+    <row r="63" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N63" s="3">
         <v>5</v>
       </c>
       <c r="O63" s="3"/>
       <c r="P63" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Q63" s="3">
         <v>1</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="T63" s="3">
         <v>1</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3"/>
@@ -5381,58 +5470,59 @@
       <c r="AJ63" s="3"/>
       <c r="AK63" s="3"/>
       <c r="AL63" s="3"/>
-    </row>
-    <row r="64" spans="1:38" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM63" s="3"/>
+    </row>
+    <row r="64" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N64" s="3">
         <v>4</v>
       </c>
       <c r="O64" s="3"/>
       <c r="P64" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Q64" s="3">
         <v>1</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="T64" s="3">
         <v>1</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3"/>
@@ -5451,58 +5541,59 @@
       <c r="AJ64" s="3"/>
       <c r="AK64" s="3"/>
       <c r="AL64" s="3"/>
-    </row>
-    <row r="65" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM64" s="3"/>
+    </row>
+    <row r="65" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K65" s="3"/>
       <c r="L65" s="3" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N65" s="3">
         <v>3</v>
       </c>
       <c r="O65" s="3"/>
       <c r="P65" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="Q65" s="3">
         <v>1</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="T65" s="3">
         <v>1</v>
       </c>
       <c r="U65" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
@@ -5521,56 +5612,57 @@
       <c r="AJ65" s="3"/>
       <c r="AK65" s="3"/>
       <c r="AL65" s="3"/>
-    </row>
-    <row r="66" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM65" s="3"/>
+    </row>
+    <row r="66" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I66" s="3"/>
       <c r="J66" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K66" s="3"/>
       <c r="L66" s="3" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
       <c r="P66" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q66" s="3">
         <v>1</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T66" s="3">
         <v>1</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V66" s="3"/>
       <c r="W66" s="3"/>
@@ -5582,10 +5674,10 @@
       <c r="AC66" s="3"/>
       <c r="AD66" s="3"/>
       <c r="AE66" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AF66" s="3" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="AG66" s="3"/>
       <c r="AH66" s="3"/>
@@ -5593,68 +5685,69 @@
       <c r="AJ66" s="3"/>
       <c r="AK66" s="3"/>
       <c r="AL66" s="3"/>
-      <c r="AM66" s="5">
+      <c r="AM66" s="3"/>
+      <c r="AN66" s="5">
         <v>0.27500000000000002</v>
       </c>
-      <c r="AN66" s="5">
+      <c r="AO66" s="5">
         <v>7.2039999999999997</v>
       </c>
-      <c r="AO66" s="5">
-        <v>39</v>
-      </c>
       <c r="AP66" s="5">
+        <v>39</v>
+      </c>
+      <c r="AQ66" s="5">
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="67" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="I67" s="3"/>
       <c r="J67" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K67" s="3"/>
       <c r="L67" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q67" s="3">
         <v>1</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="T67" s="3">
         <v>1</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
@@ -5666,10 +5759,10 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="AF67" s="3" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
@@ -5677,68 +5770,69 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
-      <c r="AM67" s="5">
+      <c r="AM67" s="3"/>
+      <c r="AN67" s="5">
         <v>0.41099999999999998</v>
       </c>
-      <c r="AN67" s="5">
+      <c r="AO67" s="5">
         <v>7.2039999999999997</v>
       </c>
-      <c r="AO67" s="5">
+      <c r="AP67" s="5">
         <v>58.4</v>
       </c>
-      <c r="AP67" s="5">
+      <c r="AQ67" s="5">
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="68" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="3" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N68" s="3"/>
       <c r="O68" s="3"/>
       <c r="P68" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q68" s="3">
         <v>30</v>
       </c>
       <c r="R68" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S68" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T68" s="3">
+        <v>1</v>
+      </c>
+      <c r="U68" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S68" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T68" s="3">
-        <v>1</v>
-      </c>
-      <c r="U68" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
@@ -5750,10 +5844,10 @@
       <c r="AC68" s="3"/>
       <c r="AD68" s="3"/>
       <c r="AE68" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AF68" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="AG68" s="3"/>
       <c r="AH68" s="3"/>
@@ -5761,56 +5855,86 @@
       <c r="AJ68" s="3"/>
       <c r="AK68" s="3"/>
       <c r="AL68" s="3"/>
-    </row>
-    <row r="69" spans="1:42" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="AM68" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AN68" s="5">
+        <v>5.7700000000000001E-2</v>
+      </c>
+      <c r="AO68" s="5">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AP68" s="5">
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="AQ68" s="5">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AR68" s="5">
+        <v>1</v>
+      </c>
+      <c r="AS68" s="5">
+        <v>2.85</v>
+      </c>
+      <c r="AT68" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="AU68" s="5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AV68" s="5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="N69" s="3"/>
       <c r="O69" s="3"/>
       <c r="P69" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="Q69" s="3">
         <v>30</v>
       </c>
       <c r="R69" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="S69" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="T69" s="3">
+        <v>1</v>
+      </c>
+      <c r="U69" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="S69" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="T69" s="3">
-        <v>1</v>
-      </c>
-      <c r="U69" s="3" t="s">
-        <v>49</v>
       </c>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
@@ -5822,10 +5946,10 @@
       <c r="AC69" s="3"/>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="AF69" s="3" t="s">
-        <v>132</v>
+        <v>154</v>
       </c>
       <c r="AG69" s="3"/>
       <c r="AH69" s="3"/>
@@ -5833,6 +5957,36 @@
       <c r="AJ69" s="3"/>
       <c r="AK69" s="3"/>
       <c r="AL69" s="3"/>
+      <c r="AM69" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="AN69" s="5">
+        <v>5.7700000000000001E-2</v>
+      </c>
+      <c r="AO69" s="5">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AP69" s="5">
+        <v>2.4870000000000001</v>
+      </c>
+      <c r="AQ69" s="5">
+        <v>7.6879999999999997</v>
+      </c>
+      <c r="AR69" s="5">
+        <v>1</v>
+      </c>
+      <c r="AS69" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="AT69" s="5">
+        <v>2.8000000000000001E-2</v>
+      </c>
+      <c r="AU69" s="5">
+        <v>25</v>
+      </c>
+      <c r="AV69" s="5">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/inst/extdata/northern_cheyenne_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/northern_cheyenne_tribe_criteria_crosswalk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="13_ncr:1_{67033712-198A-4757-B500-AE2A7181765C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{485F0FB6-F39B-4C36-9213-59E490224E28}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{67033712-198A-4757-B500-AE2A7181765C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0249FB1-CE65-47BC-84EB-ED29D10EF81C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{E55A9BC7-10AB-4EF2-8E95-202746609CFA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E55A9BC7-10AB-4EF2-8E95-202746609CFA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="855" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="161">
   <si>
     <t>TADA.ComparableDataIdentifier</t>
   </si>
@@ -476,9 +476,6 @@
     <t>pHDirection</t>
   </si>
   <si>
-    <t>TemperatureExtreme</t>
-  </si>
-  <si>
     <t>MinEqMagnitude</t>
   </si>
   <si>
@@ -503,13 +500,25 @@
     <t>((0.0577/(1+10^(7.688-pH))) + (2.487/(1+10^(pH-7.688)))) * 1.45*10^(0.028*(25-max(Temperature,7)))</t>
   </si>
   <si>
-    <t>Min</t>
-  </si>
-  <si>
-    <t>Max</t>
-  </si>
-  <si>
     <t>Equation</t>
+  </si>
+  <si>
+    <t>AmmoniaEqType</t>
+  </si>
+  <si>
+    <t>pH_param_10</t>
+  </si>
+  <si>
+    <t>pH_param_11</t>
+  </si>
+  <si>
+    <t>pH_param_12</t>
+  </si>
+  <si>
+    <t>Min Multiplier</t>
+  </si>
+  <si>
+    <t>Max Exponent</t>
   </si>
 </sst>
 </file>
@@ -915,22 +924,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88090834-75EE-4F17-A178-5F0CE015882D}">
-  <dimension ref="A1:AX69"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:BA69"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9.140625" style="5"/>
-    <col min="3" max="3" width="24.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5703125" style="5" customWidth="1"/>
-    <col min="5" max="31" width="9.140625" style="5"/>
-    <col min="32" max="32" width="102.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="19.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="8.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="2" width="9.109375" style="5"/>
+    <col min="3" max="3" width="24.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" style="5" customWidth="1"/>
+    <col min="5" max="31" width="9.109375" style="5"/>
+    <col min="32" max="32" width="102.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.5546875" style="5" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="19.6640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="8.88671875" style="5" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.109375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:53" ht="46.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1025,7 +1034,7 @@
         <v>30</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="AG1" s="1" t="s">
         <v>144</v>
@@ -1046,7 +1055,7 @@
         <v>34</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="AN1" s="1" t="s">
         <v>35</v>
@@ -1061,28 +1070,37 @@
         <v>38</v>
       </c>
       <c r="AR1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AS1" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AS1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="AU1" s="1" t="s">
+      <c r="AV1" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="AV1" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="AW1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="BA1" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="AX1" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="2" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
         <v>39</v>
@@ -1149,7 +1167,7 @@
       <c r="AL2" s="3"/>
       <c r="AM2" s="3"/>
     </row>
-    <row r="3" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
         <v>39</v>
@@ -1216,7 +1234,7 @@
       <c r="AL3" s="3"/>
       <c r="AM3" s="3"/>
     </row>
-    <row r="4" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
         <v>39</v>
@@ -1287,7 +1305,7 @@
       <c r="AL4" s="3"/>
       <c r="AM4" s="3"/>
     </row>
-    <row r="5" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
         <v>39</v>
@@ -1358,7 +1376,7 @@
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
     </row>
-    <row r="6" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
         <v>39</v>
@@ -1427,7 +1445,7 @@
       <c r="AL6" s="3"/>
       <c r="AM6" s="3"/>
     </row>
-    <row r="7" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
         <v>39</v>
@@ -1496,7 +1514,7 @@
       <c r="AL7" s="3"/>
       <c r="AM7" s="3"/>
     </row>
-    <row r="8" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
         <v>39</v>
@@ -1576,7 +1594,7 @@
         <v>-3.8660000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
         <v>39</v>
@@ -1654,7 +1672,7 @@
         <v>3.7256</v>
       </c>
     </row>
-    <row r="10" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
         <v>39</v>
@@ -1732,7 +1750,7 @@
         <v>0.68479999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
         <v>39</v>
@@ -1803,7 +1821,7 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
         <v>39</v>
@@ -1874,7 +1892,7 @@
       <c r="AL12" s="3"/>
       <c r="AM12" s="3"/>
     </row>
-    <row r="13" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
         <v>39</v>
@@ -1943,7 +1961,7 @@
       <c r="AL13" s="3"/>
       <c r="AM13" s="3"/>
     </row>
-    <row r="14" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
         <v>39</v>
@@ -2023,7 +2041,7 @@
         <v>-1.46</v>
       </c>
     </row>
-    <row r="15" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
         <v>39</v>
@@ -2103,7 +2121,7 @@
         <v>-4.7050000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:50" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
         <v>39</v>
@@ -2174,7 +2192,7 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -2243,7 +2261,7 @@
       <c r="AL17" s="3"/>
       <c r="AM17" s="3"/>
     </row>
-    <row r="18" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -2312,7 +2330,7 @@
       <c r="AL18" s="3"/>
       <c r="AM18" s="3"/>
     </row>
-    <row r="19" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -2379,7 +2397,7 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
         <v>39</v>
@@ -2446,7 +2464,7 @@
       <c r="AL20" s="3"/>
       <c r="AM20" s="3"/>
     </row>
-    <row r="21" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
         <v>39</v>
@@ -2524,7 +2542,7 @@
         <v>2.2549999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
         <v>39</v>
@@ -2602,7 +2620,7 @@
         <v>5.8400000000000001E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
         <v>39</v>
@@ -2671,7 +2689,7 @@
       <c r="AL23" s="3"/>
       <c r="AM23" s="3"/>
     </row>
-    <row r="24" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
         <v>39</v>
@@ -2740,7 +2758,7 @@
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
     </row>
-    <row r="25" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
         <v>39</v>
@@ -2813,7 +2831,7 @@
       <c r="AL25" s="3"/>
       <c r="AM25" s="3"/>
     </row>
-    <row r="26" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
         <v>39</v>
@@ -2886,7 +2904,7 @@
       <c r="AL26" s="3"/>
       <c r="AM26" s="3"/>
     </row>
-    <row r="27" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
         <v>39</v>
@@ -2955,7 +2973,7 @@
       <c r="AL27" s="3"/>
       <c r="AM27" s="3"/>
     </row>
-    <row r="28" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
         <v>39</v>
@@ -3024,7 +3042,7 @@
       <c r="AL28" s="3"/>
       <c r="AM28" s="3"/>
     </row>
-    <row r="29" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
         <v>39</v>
@@ -3102,7 +3120,7 @@
         <v>-6.59</v>
       </c>
     </row>
-    <row r="30" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
         <v>39</v>
@@ -3168,7 +3186,7 @@
       <c r="AK30" s="3"/>
       <c r="AL30" s="3"/>
     </row>
-    <row r="31" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
         <v>39</v>
@@ -3234,7 +3252,7 @@
       <c r="AK31" s="3"/>
       <c r="AL31" s="3"/>
     </row>
-    <row r="32" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
         <v>39</v>
@@ -3312,7 +3330,7 @@
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
         <v>39</v>
@@ -3390,7 +3408,7 @@
         <v>0.88400000000000001</v>
       </c>
     </row>
-    <row r="34" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
         <v>39</v>
@@ -3459,7 +3477,7 @@
       <c r="AL34" s="3"/>
       <c r="AM34" s="3"/>
     </row>
-    <row r="35" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
         <v>39</v>
@@ -3528,7 +3546,7 @@
       <c r="AL35" s="3"/>
       <c r="AM35" s="3"/>
     </row>
-    <row r="36" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
         <v>39</v>
@@ -3599,7 +3617,7 @@
       <c r="AL36" s="3"/>
       <c r="AM36" s="3"/>
     </row>
-    <row r="37" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
         <v>39</v>
@@ -3670,7 +3688,7 @@
       <c r="AL37" s="3"/>
       <c r="AM37" s="3"/>
     </row>
-    <row r="38" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
         <v>39</v>
@@ -3739,7 +3757,7 @@
       <c r="AL38" s="3"/>
       <c r="AM38" s="3"/>
     </row>
-    <row r="39" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
         <v>39</v>
@@ -3808,7 +3826,7 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
         <v>39</v>
@@ -3875,7 +3893,7 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
         <v>39</v>
@@ -3944,7 +3962,7 @@
       <c r="AL41" s="3"/>
       <c r="AM41" s="3"/>
     </row>
-    <row r="42" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
         <v>39</v>
@@ -4013,7 +4031,7 @@
       <c r="AL42" s="3"/>
       <c r="AM42" s="3"/>
     </row>
-    <row r="43" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
         <v>39</v>
@@ -4082,7 +4100,7 @@
       <c r="AL43" s="3"/>
       <c r="AM43" s="3"/>
     </row>
-    <row r="44" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
         <v>39</v>
@@ -4149,7 +4167,7 @@
       <c r="AL44" s="3"/>
       <c r="AM44" s="3"/>
     </row>
-    <row r="45" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
         <v>39</v>
@@ -4218,7 +4236,7 @@
       <c r="AL45" s="3"/>
       <c r="AM45" s="3"/>
     </row>
-    <row r="46" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
         <v>39</v>
@@ -4287,7 +4305,7 @@
       <c r="AL46" s="3"/>
       <c r="AM46" s="3"/>
     </row>
-    <row r="47" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
         <v>39</v>
@@ -4358,7 +4376,7 @@
       <c r="AL47" s="3"/>
       <c r="AM47" s="3"/>
     </row>
-    <row r="48" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
         <v>39</v>
@@ -4429,7 +4447,7 @@
       <c r="AL48" s="3"/>
       <c r="AM48" s="3"/>
     </row>
-    <row r="49" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
         <v>39</v>
@@ -4498,7 +4516,7 @@
       <c r="AL49" s="3"/>
       <c r="AM49" s="3"/>
     </row>
-    <row r="50" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
         <v>39</v>
@@ -4565,7 +4583,7 @@
       <c r="AL50" s="3"/>
       <c r="AM50" s="3"/>
     </row>
-    <row r="51" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
         <v>39</v>
@@ -4632,7 +4650,7 @@
       <c r="AL51" s="3"/>
       <c r="AM51" s="3"/>
     </row>
-    <row r="52" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
         <v>39</v>
@@ -4699,7 +4717,7 @@
       <c r="AL52" s="3"/>
       <c r="AM52" s="3"/>
     </row>
-    <row r="53" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
         <v>39</v>
@@ -4766,7 +4784,7 @@
       <c r="AL53" s="3"/>
       <c r="AM53" s="3"/>
     </row>
-    <row r="54" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
         <v>39</v>
@@ -4835,7 +4853,7 @@
       <c r="AL54" s="3"/>
       <c r="AM54" s="3"/>
     </row>
-    <row r="55" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
         <v>39</v>
@@ -4904,7 +4922,7 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
         <v>39</v>
@@ -4975,7 +4993,7 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
         <v>39</v>
@@ -5046,7 +5064,7 @@
       <c r="AL57" s="3"/>
       <c r="AM57" s="3"/>
     </row>
-    <row r="58" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
         <v>39</v>
@@ -5117,7 +5135,7 @@
       <c r="AL58" s="3"/>
       <c r="AM58" s="3"/>
     </row>
-    <row r="59" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
         <v>39</v>
@@ -5188,7 +5206,7 @@
       <c r="AL59" s="3"/>
       <c r="AM59" s="3"/>
     </row>
-    <row r="60" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
         <v>39</v>
@@ -5259,7 +5277,7 @@
       <c r="AL60" s="3"/>
       <c r="AM60" s="3"/>
     </row>
-    <row r="61" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
         <v>39</v>
@@ -5330,7 +5348,7 @@
       <c r="AL61" s="3"/>
       <c r="AM61" s="3"/>
     </row>
-    <row r="62" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
         <v>39</v>
@@ -5401,7 +5419,7 @@
       <c r="AL62" s="3"/>
       <c r="AM62" s="3"/>
     </row>
-    <row r="63" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
         <v>39</v>
@@ -5472,7 +5490,7 @@
       <c r="AL63" s="3"/>
       <c r="AM63" s="3"/>
     </row>
-    <row r="64" spans="1:39" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
         <v>39</v>
@@ -5543,7 +5561,7 @@
       <c r="AL64" s="3"/>
       <c r="AM64" s="3"/>
     </row>
-    <row r="65" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
         <v>39</v>
@@ -5614,7 +5632,7 @@
       <c r="AL65" s="3"/>
       <c r="AM65" s="3"/>
     </row>
-    <row r="66" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
         <v>39</v>
@@ -5699,7 +5717,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="67" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
         <v>39</v>
@@ -5784,7 +5802,7 @@
         <v>7.2039999999999997</v>
       </c>
     </row>
-    <row r="68" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
         <v>39</v>
@@ -5856,7 +5874,7 @@
       <c r="AK68" s="3"/>
       <c r="AL68" s="3"/>
       <c r="AM68" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="AN68" s="5">
         <v>5.7700000000000001E-2</v>
@@ -5886,7 +5904,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:48" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
         <v>39</v>
@@ -5949,7 +5967,7 @@
         <v>125</v>
       </c>
       <c r="AF69" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="AG69" s="3"/>
       <c r="AH69" s="3"/>
@@ -5958,7 +5976,7 @@
       <c r="AK69" s="3"/>
       <c r="AL69" s="3"/>
       <c r="AM69" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="AN69" s="5">
         <v>5.7700000000000001E-2</v>

--- a/inst/extdata/northern_cheyenne_tribe_criteria_crosswalk.xlsx
+++ b/inst/extdata/northern_cheyenne_tribe_criteria_crosswalk.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tetratechinc-my.sharepoint.com/personal/hannah_ferriby_tetratech_com/Documents/Documents/GitHub/TADACommunityHub/inst/extdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="13_ncr:1_{67033712-198A-4757-B500-AE2A7181765C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0249FB1-CE65-47BC-84EB-ED29D10EF81C}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{67033712-198A-4757-B500-AE2A7181765C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D5A0858-9EFC-415E-B39B-D9DA1567833F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{E55A9BC7-10AB-4EF2-8E95-202746609CFA}"/>
   </bookViews>
@@ -101,18 +101,12 @@
     <t>FreqMethod</t>
   </si>
   <si>
-    <t>AssessPeriod</t>
-  </si>
-  <si>
     <t>AssessPeriodStartDate</t>
   </si>
   <si>
     <t>AssessPeriodEndDate</t>
   </si>
   <si>
-    <t>Season</t>
-  </si>
-  <si>
     <t>SeasonStartDate</t>
   </si>
   <si>
@@ -519,6 +513,12 @@
   </si>
   <si>
     <t>Max Exponent</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Links</t>
   </si>
 </sst>
 </file>
@@ -1025,135 +1025,135 @@
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="AE1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="AI1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="1" t="s">
+      <c r="AJ1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="1" t="s">
+      <c r="AK1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="AL1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="AW1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AX1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="AH1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="AI1" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AJ1" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AK1" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="AL1" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AM1" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N2" s="3"/>
       <c r="O2" s="3">
         <v>5.6</v>
       </c>
       <c r="P2" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q2" s="3">
-        <v>1</v>
-      </c>
-      <c r="R2" s="3" t="s">
+      <c r="T2" s="3">
+        <v>1</v>
+      </c>
+      <c r="U2" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T2" s="3">
-        <v>1</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="4"/>
-      <c r="AA2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
       <c r="AB2" s="3"/>
       <c r="AC2" s="3"/>
       <c r="AD2" s="3"/>
@@ -1170,57 +1170,57 @@
     <row r="3" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>41</v>
       </c>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N3" s="3"/>
       <c r="O3" s="3">
         <v>640</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q3" s="3">
         <v>30</v>
       </c>
       <c r="R3" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T3" s="3">
+        <v>1</v>
+      </c>
+      <c r="U3" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T3" s="3">
-        <v>1</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3"/>
-      <c r="X3" s="3"/>
-      <c r="Y3" s="3"/>
-      <c r="Z3" s="4"/>
-      <c r="AA3" s="4"/>
+      <c r="X3" s="4"/>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
       <c r="AB3" s="3"/>
       <c r="AC3" s="3"/>
       <c r="AD3" s="3"/>
@@ -1237,61 +1237,61 @@
     <row r="4" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N4" s="3"/>
       <c r="O4" s="3">
         <v>340</v>
       </c>
       <c r="P4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q4" s="3">
-        <v>1</v>
-      </c>
-      <c r="R4" s="3" t="s">
+      <c r="T4" s="3">
+        <v>1</v>
+      </c>
+      <c r="U4" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T4" s="3">
-        <v>1</v>
-      </c>
-      <c r="U4" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="4"/>
-      <c r="AA4" s="4"/>
+      <c r="X4" s="4"/>
+      <c r="Y4" s="4"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
       <c r="AB4" s="3"/>
       <c r="AC4" s="3"/>
       <c r="AD4" s="3"/>
@@ -1308,61 +1308,61 @@
     <row r="5" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N5" s="3"/>
       <c r="O5" s="3">
         <v>150</v>
       </c>
       <c r="P5" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q5" s="3">
         <v>30</v>
       </c>
       <c r="R5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T5" s="3">
+        <v>1</v>
+      </c>
+      <c r="U5" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S5" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T5" s="3">
-        <v>1</v>
-      </c>
-      <c r="U5" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="4"/>
-      <c r="AA5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="Z5" s="3"/>
+      <c r="AA5" s="3"/>
       <c r="AB5" s="3"/>
       <c r="AC5" s="3"/>
       <c r="AD5" s="3"/>
@@ -1379,59 +1379,59 @@
     <row r="6" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3">
         <v>1.7999999999999999E-2</v>
       </c>
       <c r="P6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>1</v>
+      </c>
+      <c r="R6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q6" s="3">
-        <v>1</v>
-      </c>
-      <c r="R6" s="3" t="s">
+      <c r="T6" s="3">
+        <v>1</v>
+      </c>
+      <c r="U6" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S6" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T6" s="3">
-        <v>1</v>
-      </c>
-      <c r="U6" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="4"/>
-      <c r="AA6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4"/>
+      <c r="Z6" s="3"/>
+      <c r="AA6" s="3"/>
       <c r="AB6" s="3"/>
       <c r="AC6" s="3"/>
       <c r="AD6" s="3"/>
@@ -1448,59 +1448,59 @@
     <row r="7" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3">
         <v>0.14000000000000001</v>
       </c>
       <c r="P7" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q7" s="3">
         <v>30</v>
       </c>
       <c r="R7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S7" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T7" s="3">
+        <v>1</v>
+      </c>
+      <c r="U7" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T7" s="3">
-        <v>1</v>
-      </c>
-      <c r="U7" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V7" s="3"/>
       <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
       <c r="AB7" s="3"/>
       <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
@@ -1517,67 +1517,67 @@
     <row r="8" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>55</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I8" s="3"/>
       <c r="J8" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
       <c r="P8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>1</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S8" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q8" s="3">
-        <v>1</v>
-      </c>
-      <c r="R8" s="3" t="s">
+      <c r="T8" s="3">
+        <v>1</v>
+      </c>
+      <c r="U8" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T8" s="3">
-        <v>1</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="4"/>
-      <c r="AA8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
       <c r="AB8" s="3"/>
       <c r="AC8" s="3"/>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AF8" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AG8" s="3"/>
       <c r="AH8" s="3"/>
@@ -1597,67 +1597,67 @@
     <row r="9" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>1</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S9" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q9" s="3">
-        <v>1</v>
-      </c>
-      <c r="R9" s="3" t="s">
+      <c r="T9" s="3">
+        <v>1</v>
+      </c>
+      <c r="U9" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T9" s="3">
-        <v>1</v>
-      </c>
-      <c r="U9" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="4"/>
-      <c r="AA9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
       <c r="AB9" s="3"/>
       <c r="AC9" s="3"/>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AF9" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AG9" s="3"/>
       <c r="AH9" s="3"/>
@@ -1675,67 +1675,67 @@
     <row r="10" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
       <c r="P10" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q10" s="3">
         <v>30</v>
       </c>
       <c r="R10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T10" s="3">
+        <v>1</v>
+      </c>
+      <c r="U10" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T10" s="3">
-        <v>1</v>
-      </c>
-      <c r="U10" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
       <c r="AB10" s="3"/>
       <c r="AC10" s="3"/>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AF10" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AG10" s="3"/>
       <c r="AH10" s="3"/>
@@ -1753,61 +1753,61 @@
     <row r="11" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3">
         <v>16</v>
       </c>
       <c r="P11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>1</v>
+      </c>
+      <c r="R11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q11" s="3">
-        <v>1</v>
-      </c>
-      <c r="R11" s="3" t="s">
+      <c r="T11" s="3">
+        <v>1</v>
+      </c>
+      <c r="U11" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T11" s="3">
-        <v>1</v>
-      </c>
-      <c r="U11" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="4"/>
-      <c r="AA11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
@@ -1824,61 +1824,61 @@
     <row r="12" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N12" s="3"/>
       <c r="O12" s="3">
         <v>11</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q12" s="3">
         <v>30</v>
       </c>
       <c r="R12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T12" s="3">
+        <v>1</v>
+      </c>
+      <c r="U12" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T12" s="3">
-        <v>1</v>
-      </c>
-      <c r="U12" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="4"/>
-      <c r="AA12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
       <c r="AB12" s="3"/>
       <c r="AC12" s="3"/>
       <c r="AD12" s="3"/>
@@ -1895,59 +1895,59 @@
     <row r="13" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N13" s="3"/>
       <c r="O13" s="3">
         <v>1300</v>
       </c>
       <c r="P13" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>1</v>
+      </c>
+      <c r="R13" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S13" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q13" s="3">
-        <v>1</v>
-      </c>
-      <c r="R13" s="3" t="s">
+      <c r="T13" s="3">
+        <v>1</v>
+      </c>
+      <c r="U13" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T13" s="3">
-        <v>1</v>
-      </c>
-      <c r="U13" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="4"/>
-      <c r="AA13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
       <c r="AB13" s="3"/>
       <c r="AC13" s="3"/>
       <c r="AD13" s="3"/>
@@ -1964,67 +1964,67 @@
     <row r="14" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I14" s="3"/>
       <c r="J14" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
       <c r="P14" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>1</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q14" s="3">
-        <v>1</v>
-      </c>
-      <c r="R14" s="3" t="s">
+      <c r="T14" s="3">
+        <v>1</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T14" s="3">
-        <v>1</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="4"/>
-      <c r="AA14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4"/>
+      <c r="Z14" s="3"/>
+      <c r="AA14" s="3"/>
       <c r="AB14" s="3"/>
       <c r="AC14" s="3"/>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AF14" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AG14" s="3"/>
       <c r="AH14" s="3"/>
@@ -2044,67 +2044,67 @@
     <row r="15" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I15" s="3"/>
       <c r="J15" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q15" s="3">
         <v>30</v>
       </c>
       <c r="R15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T15" s="3">
+        <v>1</v>
+      </c>
+      <c r="U15" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T15" s="3">
-        <v>1</v>
-      </c>
-      <c r="U15" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="4"/>
-      <c r="AA15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4"/>
+      <c r="Z15" s="3"/>
+      <c r="AA15" s="3"/>
       <c r="AB15" s="3"/>
       <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AF15" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AG15" s="3"/>
       <c r="AH15" s="3"/>
@@ -2124,61 +2124,61 @@
     <row r="16" spans="1:53" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N16" s="3"/>
       <c r="O16" s="3">
         <v>1.4</v>
       </c>
       <c r="P16" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q16" s="3">
+        <v>1</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S16" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q16" s="3">
-        <v>1</v>
-      </c>
-      <c r="R16" s="3" t="s">
+      <c r="T16" s="3">
+        <v>1</v>
+      </c>
+      <c r="U16" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T16" s="3">
-        <v>1</v>
-      </c>
-      <c r="U16" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4"/>
+      <c r="Z16" s="3"/>
+      <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
@@ -2195,59 +2195,59 @@
     <row r="17" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N17" s="3"/>
       <c r="O17" s="3">
         <v>0.05</v>
       </c>
       <c r="P17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>1</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q17" s="3">
-        <v>1</v>
-      </c>
-      <c r="R17" s="3" t="s">
+      <c r="T17" s="3">
+        <v>1</v>
+      </c>
+      <c r="U17" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T17" s="3">
-        <v>1</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="4"/>
-      <c r="AA17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
       <c r="AB17" s="3"/>
       <c r="AC17" s="3"/>
       <c r="AD17" s="3"/>
@@ -2264,59 +2264,59 @@
     <row r="18" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N18" s="3"/>
       <c r="O18" s="3">
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q18" s="3">
         <v>30</v>
       </c>
       <c r="R18" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T18" s="3">
+        <v>1</v>
+      </c>
+      <c r="U18" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T18" s="3">
-        <v>1</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="4"/>
-      <c r="AA18" s="4"/>
+      <c r="X18" s="4"/>
+      <c r="Y18" s="4"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
       <c r="AB18" s="3"/>
       <c r="AC18" s="3"/>
       <c r="AD18" s="3"/>
@@ -2333,57 +2333,57 @@
     <row r="19" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N19" s="3"/>
       <c r="O19" s="3">
         <v>0.3</v>
       </c>
       <c r="P19" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q19" s="3">
         <v>30</v>
       </c>
       <c r="R19" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S19" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T19" s="3">
+        <v>1</v>
+      </c>
+      <c r="U19" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S19" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T19" s="3">
-        <v>1</v>
-      </c>
-      <c r="U19" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="4"/>
-      <c r="AA19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
@@ -2400,57 +2400,57 @@
     <row r="20" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N20" s="3"/>
       <c r="O20" s="3">
         <v>0.3</v>
       </c>
       <c r="P20" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q20" s="3">
         <v>30</v>
       </c>
       <c r="R20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T20" s="3">
+        <v>1</v>
+      </c>
+      <c r="U20" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T20" s="3">
-        <v>1</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="4"/>
-      <c r="AA20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="4"/>
+      <c r="Z20" s="3"/>
+      <c r="AA20" s="3"/>
       <c r="AB20" s="3"/>
       <c r="AC20" s="3"/>
       <c r="AD20" s="3"/>
@@ -2467,67 +2467,67 @@
     <row r="21" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
       <c r="P21" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q21" s="3">
+        <v>1</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S21" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q21" s="3">
-        <v>1</v>
-      </c>
-      <c r="R21" s="3" t="s">
+      <c r="T21" s="3">
+        <v>1</v>
+      </c>
+      <c r="U21" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S21" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T21" s="3">
-        <v>1</v>
-      </c>
-      <c r="U21" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="4"/>
-      <c r="AA21" s="4"/>
+      <c r="X21" s="4"/>
+      <c r="Y21" s="4"/>
+      <c r="Z21" s="3"/>
+      <c r="AA21" s="3"/>
       <c r="AB21" s="3"/>
       <c r="AC21" s="3"/>
       <c r="AD21" s="3"/>
       <c r="AE21" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AF21" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AG21" s="3"/>
       <c r="AH21" s="3"/>
@@ -2545,67 +2545,67 @@
     <row r="22" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
       <c r="P22" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q22" s="3">
         <v>30</v>
       </c>
       <c r="R22" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T22" s="3">
+        <v>1</v>
+      </c>
+      <c r="U22" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T22" s="3">
-        <v>1</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="4"/>
-      <c r="AA22" s="4"/>
+      <c r="X22" s="4"/>
+      <c r="Y22" s="4"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
       <c r="AB22" s="3"/>
       <c r="AC22" s="3"/>
       <c r="AD22" s="3"/>
       <c r="AE22" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AF22" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="AG22" s="3"/>
       <c r="AH22" s="3"/>
@@ -2623,59 +2623,59 @@
     <row r="23" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N23" s="3"/>
       <c r="O23" s="3">
         <v>610</v>
       </c>
       <c r="P23" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q23" s="3">
+        <v>1</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S23" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q23" s="3">
-        <v>1</v>
-      </c>
-      <c r="R23" s="3" t="s">
+      <c r="T23" s="3">
+        <v>1</v>
+      </c>
+      <c r="U23" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T23" s="3">
-        <v>1</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="4"/>
-      <c r="AA23" s="4"/>
+      <c r="X23" s="4"/>
+      <c r="Y23" s="4"/>
+      <c r="Z23" s="3"/>
+      <c r="AA23" s="3"/>
       <c r="AB23" s="3"/>
       <c r="AC23" s="3"/>
       <c r="AD23" s="3"/>
@@ -2692,59 +2692,59 @@
     <row r="24" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
       <c r="J24" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N24" s="3"/>
       <c r="O24" s="3">
         <v>4600</v>
       </c>
       <c r="P24" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q24" s="3">
         <v>30</v>
       </c>
       <c r="R24" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T24" s="3">
+        <v>1</v>
+      </c>
+      <c r="U24" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T24" s="3">
-        <v>1</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="4"/>
-      <c r="AA24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="3"/>
+      <c r="AA24" s="3"/>
       <c r="AB24" s="3"/>
       <c r="AC24" s="3"/>
       <c r="AD24" s="3"/>
@@ -2761,63 +2761,63 @@
     <row r="25" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N25" s="3"/>
       <c r="O25" s="3">
         <v>1.5</v>
       </c>
       <c r="P25" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q25" s="3">
         <v>30</v>
       </c>
       <c r="R25" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S25" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T25" s="3">
+        <v>1</v>
+      </c>
+      <c r="U25" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S25" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T25" s="3">
-        <v>1</v>
-      </c>
-      <c r="U25" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="4"/>
-      <c r="AA25" s="4"/>
+      <c r="X25" s="4"/>
+      <c r="Y25" s="4"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
       <c r="AB25" s="3"/>
       <c r="AC25" s="3"/>
       <c r="AD25" s="3"/>
@@ -2834,63 +2834,63 @@
     <row r="26" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N26" s="3"/>
       <c r="O26" s="3">
         <v>3.1</v>
       </c>
       <c r="P26" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q26" s="3">
         <v>30</v>
       </c>
       <c r="R26" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T26" s="3">
+        <v>1</v>
+      </c>
+      <c r="U26" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T26" s="3">
-        <v>1</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="4"/>
-      <c r="AA26" s="4"/>
+      <c r="X26" s="4"/>
+      <c r="Y26" s="4"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
       <c r="AB26" s="3"/>
       <c r="AC26" s="3"/>
       <c r="AD26" s="3"/>
@@ -2907,59 +2907,59 @@
     <row r="27" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3">
         <v>170</v>
       </c>
       <c r="P27" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q27" s="3">
+        <v>1</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S27" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q27" s="3">
-        <v>1</v>
-      </c>
-      <c r="R27" s="3" t="s">
+      <c r="T27" s="3">
+        <v>1</v>
+      </c>
+      <c r="U27" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T27" s="3">
-        <v>1</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V27" s="3"/>
       <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="4"/>
-      <c r="AA27" s="4"/>
+      <c r="X27" s="4"/>
+      <c r="Y27" s="4"/>
+      <c r="Z27" s="3"/>
+      <c r="AA27" s="3"/>
       <c r="AB27" s="3"/>
       <c r="AC27" s="3"/>
       <c r="AD27" s="3"/>
@@ -2976,59 +2976,59 @@
     <row r="28" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G28" s="3"/>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3">
         <v>4200</v>
       </c>
       <c r="P28" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q28" s="3">
         <v>30</v>
       </c>
       <c r="R28" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T28" s="3">
+        <v>1</v>
+      </c>
+      <c r="U28" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S28" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T28" s="3">
-        <v>1</v>
-      </c>
-      <c r="U28" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="4"/>
-      <c r="AA28" s="4"/>
+      <c r="X28" s="4"/>
+      <c r="Y28" s="4"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
       <c r="AB28" s="3"/>
       <c r="AC28" s="3"/>
       <c r="AD28" s="3"/>
@@ -3045,67 +3045,67 @@
     <row r="29" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q29" s="3">
+        <v>1</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S29" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q29" s="3">
-        <v>1</v>
-      </c>
-      <c r="R29" s="3" t="s">
+      <c r="T29" s="3">
+        <v>1</v>
+      </c>
+      <c r="U29" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T29" s="3">
-        <v>1</v>
-      </c>
-      <c r="U29" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V29" s="3"/>
       <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="4"/>
-      <c r="AA29" s="4"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="3"/>
       <c r="AB29" s="3"/>
       <c r="AC29" s="3"/>
       <c r="AD29" s="3"/>
       <c r="AE29" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AF29" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AG29" s="3"/>
       <c r="AH29" s="3"/>
@@ -3123,57 +3123,57 @@
     <row r="30" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
       <c r="J30" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3">
         <v>0.24</v>
       </c>
       <c r="P30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>1</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S30" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q30" s="3">
-        <v>1</v>
-      </c>
-      <c r="R30" s="3" t="s">
+      <c r="T30" s="3">
+        <v>1</v>
+      </c>
+      <c r="U30" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S30" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T30" s="3">
-        <v>1</v>
-      </c>
-      <c r="U30" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
-      <c r="Z30" s="4"/>
-      <c r="AA30" s="4"/>
+      <c r="X30" s="4"/>
+      <c r="Y30" s="4"/>
+      <c r="Z30" s="3"/>
+      <c r="AA30" s="3"/>
       <c r="AB30" s="3"/>
       <c r="AC30" s="3"/>
       <c r="AD30" s="3"/>
@@ -3189,57 +3189,57 @@
     <row r="31" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
       <c r="J31" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3">
         <v>0.47</v>
       </c>
       <c r="P31" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q31" s="3">
         <v>30</v>
       </c>
       <c r="R31" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S31" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T31" s="3">
+        <v>1</v>
+      </c>
+      <c r="U31" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S31" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T31" s="3">
-        <v>1</v>
-      </c>
-      <c r="U31" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V31" s="3"/>
       <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="4"/>
-      <c r="AA31" s="4"/>
+      <c r="X31" s="4"/>
+      <c r="Y31" s="4"/>
+      <c r="Z31" s="3"/>
+      <c r="AA31" s="3"/>
       <c r="AB31" s="3"/>
       <c r="AC31" s="3"/>
       <c r="AD31" s="3"/>
@@ -3255,67 +3255,67 @@
     <row r="32" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>1</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S32" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q32" s="3">
-        <v>1</v>
-      </c>
-      <c r="R32" s="3" t="s">
+      <c r="T32" s="3">
+        <v>1</v>
+      </c>
+      <c r="U32" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S32" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T32" s="3">
-        <v>1</v>
-      </c>
-      <c r="U32" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V32" s="3"/>
       <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="4"/>
-      <c r="AA32" s="4"/>
+      <c r="X32" s="4"/>
+      <c r="Y32" s="4"/>
+      <c r="Z32" s="3"/>
+      <c r="AA32" s="3"/>
       <c r="AB32" s="3"/>
       <c r="AC32" s="3"/>
       <c r="AD32" s="3"/>
       <c r="AE32" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AF32" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="AG32" s="3"/>
       <c r="AH32" s="3"/>
@@ -3333,67 +3333,67 @@
     <row r="33" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q33" s="3">
         <v>30</v>
       </c>
       <c r="R33" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T33" s="3">
+        <v>1</v>
+      </c>
+      <c r="U33" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T33" s="3">
-        <v>1</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="4"/>
-      <c r="AA33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4"/>
+      <c r="Z33" s="3"/>
+      <c r="AA33" s="3"/>
       <c r="AB33" s="3"/>
       <c r="AC33" s="3"/>
       <c r="AD33" s="3"/>
       <c r="AE33" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AF33" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="AG33" s="3"/>
       <c r="AH33" s="3"/>
@@ -3411,59 +3411,59 @@
     <row r="34" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G34" s="3"/>
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
       <c r="J34" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N34" s="3"/>
       <c r="O34" s="3">
         <v>7400</v>
       </c>
       <c r="P34" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>1</v>
+      </c>
+      <c r="R34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S34" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q34" s="3">
-        <v>1</v>
-      </c>
-      <c r="R34" s="3" t="s">
+      <c r="T34" s="3">
+        <v>1</v>
+      </c>
+      <c r="U34" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S34" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T34" s="3">
-        <v>1</v>
-      </c>
-      <c r="U34" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V34" s="3"/>
       <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="4"/>
-      <c r="AA34" s="4"/>
+      <c r="X34" s="4"/>
+      <c r="Y34" s="4"/>
+      <c r="Z34" s="3"/>
+      <c r="AA34" s="3"/>
       <c r="AB34" s="3"/>
       <c r="AC34" s="3"/>
       <c r="AD34" s="3"/>
@@ -3480,59 +3480,59 @@
     <row r="35" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G35" s="3"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
       <c r="J35" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N35" s="3"/>
       <c r="O35" s="3">
         <v>26000</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q35" s="3">
         <v>30</v>
       </c>
       <c r="R35" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T35" s="3">
+        <v>1</v>
+      </c>
+      <c r="U35" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T35" s="3">
-        <v>1</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="4"/>
+      <c r="X35" s="4"/>
+      <c r="Y35" s="4"/>
+      <c r="Z35" s="3"/>
+      <c r="AA35" s="3"/>
       <c r="AB35" s="3"/>
       <c r="AC35" s="3"/>
       <c r="AD35" s="3"/>
@@ -3549,61 +3549,61 @@
     <row r="36" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="G36" s="3"/>
       <c r="H36" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N36" s="3"/>
       <c r="O36" s="3">
         <v>22</v>
       </c>
       <c r="P36" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q36" s="3">
+        <v>1</v>
+      </c>
+      <c r="R36" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S36" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q36" s="3">
-        <v>1</v>
-      </c>
-      <c r="R36" s="3" t="s">
+      <c r="T36" s="3">
+        <v>1</v>
+      </c>
+      <c r="U36" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S36" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T36" s="3">
-        <v>1</v>
-      </c>
-      <c r="U36" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V36" s="3"/>
       <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="4"/>
-      <c r="AA36" s="4"/>
+      <c r="X36" s="4"/>
+      <c r="Y36" s="4"/>
+      <c r="Z36" s="3"/>
+      <c r="AA36" s="3"/>
       <c r="AB36" s="3"/>
       <c r="AC36" s="3"/>
       <c r="AD36" s="3"/>
@@ -3620,61 +3620,61 @@
     <row r="37" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>85</v>
       </c>
       <c r="G37" s="3"/>
       <c r="H37" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3">
         <v>5.2</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q37" s="3">
         <v>30</v>
       </c>
       <c r="R37" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T37" s="3">
+        <v>1</v>
+      </c>
+      <c r="U37" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S37" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T37" s="3">
-        <v>1</v>
-      </c>
-      <c r="U37" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="4"/>
-      <c r="AA37" s="4"/>
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4"/>
+      <c r="Z37" s="3"/>
+      <c r="AA37" s="3"/>
       <c r="AB37" s="3"/>
       <c r="AC37" s="3"/>
       <c r="AD37" s="3"/>
@@ -3691,59 +3691,59 @@
     <row r="38" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G38" s="3"/>
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
       <c r="J38" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3">
         <v>4</v>
       </c>
       <c r="P38" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q38" s="3">
+        <v>1</v>
+      </c>
+      <c r="R38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S38" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q38" s="3">
-        <v>1</v>
-      </c>
-      <c r="R38" s="3" t="s">
+      <c r="T38" s="3">
+        <v>1</v>
+      </c>
+      <c r="U38" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S38" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T38" s="3">
-        <v>1</v>
-      </c>
-      <c r="U38" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
-      <c r="Z38" s="4"/>
-      <c r="AA38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4"/>
+      <c r="Z38" s="3"/>
+      <c r="AA38" s="3"/>
       <c r="AB38" s="3"/>
       <c r="AC38" s="3"/>
       <c r="AD38" s="3"/>
@@ -3760,59 +3760,59 @@
     <row r="39" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3">
         <v>400</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q39" s="3">
         <v>30</v>
       </c>
       <c r="R39" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S39" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T39" s="3">
+        <v>1</v>
+      </c>
+      <c r="U39" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S39" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T39" s="3">
-        <v>1</v>
-      </c>
-      <c r="U39" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="4"/>
-      <c r="AA39" s="4"/>
+      <c r="X39" s="4"/>
+      <c r="Y39" s="4"/>
+      <c r="Z39" s="3"/>
+      <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
@@ -3829,57 +3829,57 @@
     <row r="40" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N40" s="3"/>
       <c r="O40" s="3">
         <v>7000000</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="Q40" s="3">
         <v>1</v>
       </c>
       <c r="R40" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S40" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="T40" s="3">
+        <v>1</v>
+      </c>
+      <c r="U40" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S40" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T40" s="3">
-        <v>1</v>
-      </c>
-      <c r="U40" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="4"/>
-      <c r="AA40" s="4"/>
+      <c r="X40" s="4"/>
+      <c r="Y40" s="4"/>
+      <c r="Z40" s="3"/>
+      <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
@@ -3896,59 +3896,59 @@
     <row r="41" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I41" s="3"/>
       <c r="J41" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N41" s="3"/>
       <c r="O41" s="3">
         <v>20000</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q41" s="3">
         <v>30</v>
       </c>
       <c r="R41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S41" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T41" s="3">
+        <v>1</v>
+      </c>
+      <c r="U41" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T41" s="3">
-        <v>1</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="4"/>
-      <c r="AA41" s="4"/>
+      <c r="X41" s="4"/>
+      <c r="Y41" s="4"/>
+      <c r="Z41" s="3"/>
+      <c r="AA41" s="3"/>
       <c r="AB41" s="3"/>
       <c r="AC41" s="3"/>
       <c r="AD41" s="3"/>
@@ -3965,59 +3965,59 @@
     <row r="42" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D42" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="G42" s="3"/>
       <c r="H42" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I42" s="3"/>
       <c r="J42" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N42" s="3"/>
       <c r="O42" s="3"/>
       <c r="P42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>1</v>
+      </c>
+      <c r="R42" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S42" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q42" s="3">
-        <v>1</v>
-      </c>
-      <c r="R42" s="3" t="s">
+      <c r="T42" s="3">
+        <v>1</v>
+      </c>
+      <c r="U42" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T42" s="3">
-        <v>1</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="4"/>
-      <c r="AA42" s="4"/>
+      <c r="X42" s="4"/>
+      <c r="Y42" s="4"/>
+      <c r="Z42" s="3"/>
+      <c r="AA42" s="3"/>
       <c r="AB42" s="3"/>
       <c r="AC42" s="3"/>
       <c r="AD42" s="3"/>
@@ -4034,59 +4034,59 @@
     <row r="43" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D43" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="G43" s="3"/>
       <c r="H43" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I43" s="3"/>
       <c r="J43" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N43" s="3"/>
       <c r="O43" s="3"/>
       <c r="P43" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q43" s="3">
         <v>30</v>
       </c>
       <c r="R43" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S43" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T43" s="3">
+        <v>1</v>
+      </c>
+      <c r="U43" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S43" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T43" s="3">
-        <v>1</v>
-      </c>
-      <c r="U43" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V43" s="3"/>
       <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="4"/>
-      <c r="AA43" s="4"/>
+      <c r="X43" s="4"/>
+      <c r="Y43" s="4"/>
+      <c r="Z43" s="3"/>
+      <c r="AA43" s="3"/>
       <c r="AB43" s="3"/>
       <c r="AC43" s="3"/>
       <c r="AD43" s="3"/>
@@ -4103,57 +4103,57 @@
     <row r="44" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
       <c r="J44" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N44" s="3"/>
       <c r="O44" s="3">
         <v>1000</v>
       </c>
       <c r="P44" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q44" s="3">
+        <v>1</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S44" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q44" s="3">
-        <v>1</v>
-      </c>
-      <c r="R44" s="3" t="s">
+      <c r="T44" s="3">
+        <v>1</v>
+      </c>
+      <c r="U44" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S44" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T44" s="3">
-        <v>1</v>
-      </c>
-      <c r="U44" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V44" s="3"/>
       <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="4"/>
-      <c r="AA44" s="4"/>
+      <c r="X44" s="4"/>
+      <c r="Y44" s="4"/>
+      <c r="Z44" s="3"/>
+      <c r="AA44" s="3"/>
       <c r="AB44" s="3"/>
       <c r="AC44" s="3"/>
       <c r="AD44" s="3"/>
@@ -4170,59 +4170,59 @@
     <row r="45" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
       <c r="H45" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I45" s="3"/>
       <c r="J45" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N45" s="3"/>
       <c r="O45" s="3">
         <v>860000</v>
       </c>
       <c r="P45" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>1</v>
+      </c>
+      <c r="R45" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S45" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q45" s="3">
-        <v>1</v>
-      </c>
-      <c r="R45" s="3" t="s">
+      <c r="T45" s="3">
+        <v>1</v>
+      </c>
+      <c r="U45" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S45" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T45" s="3">
-        <v>1</v>
-      </c>
-      <c r="U45" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="4"/>
-      <c r="AA45" s="4"/>
+      <c r="X45" s="4"/>
+      <c r="Y45" s="4"/>
+      <c r="Z45" s="3"/>
+      <c r="AA45" s="3"/>
       <c r="AB45" s="3"/>
       <c r="AC45" s="3"/>
       <c r="AD45" s="3"/>
@@ -4239,59 +4239,59 @@
     <row r="46" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
       <c r="H46" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I46" s="3"/>
       <c r="J46" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N46" s="3"/>
       <c r="O46" s="3">
         <v>230000</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q46" s="3">
         <v>30</v>
       </c>
       <c r="R46" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S46" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T46" s="3">
+        <v>1</v>
+      </c>
+      <c r="U46" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T46" s="3">
-        <v>1</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="4"/>
-      <c r="AA46" s="4"/>
+      <c r="X46" s="4"/>
+      <c r="Y46" s="4"/>
+      <c r="Z46" s="3"/>
+      <c r="AA46" s="3"/>
       <c r="AB46" s="3"/>
       <c r="AC46" s="3"/>
       <c r="AD46" s="3"/>
@@ -4308,61 +4308,61 @@
     <row r="47" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D47" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="G47" s="3"/>
       <c r="H47" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I47" s="3"/>
       <c r="J47" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N47" s="3"/>
       <c r="O47" s="3">
         <v>19</v>
       </c>
       <c r="P47" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>1</v>
+      </c>
+      <c r="R47" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S47" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q47" s="3">
-        <v>1</v>
-      </c>
-      <c r="R47" s="3" t="s">
+      <c r="T47" s="3">
+        <v>1</v>
+      </c>
+      <c r="U47" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S47" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T47" s="3">
-        <v>1</v>
-      </c>
-      <c r="U47" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="4"/>
-      <c r="AA47" s="4"/>
+      <c r="X47" s="4"/>
+      <c r="Y47" s="4"/>
+      <c r="Z47" s="3"/>
+      <c r="AA47" s="3"/>
       <c r="AB47" s="3"/>
       <c r="AC47" s="3"/>
       <c r="AD47" s="3"/>
@@ -4379,61 +4379,61 @@
     <row r="48" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D48" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>52</v>
       </c>
       <c r="G48" s="3"/>
       <c r="H48" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I48" s="3"/>
       <c r="J48" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N48" s="3"/>
       <c r="O48" s="3">
         <v>11</v>
       </c>
       <c r="P48" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q48" s="3">
         <v>30</v>
       </c>
       <c r="R48" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S48" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T48" s="3">
+        <v>1</v>
+      </c>
+      <c r="U48" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S48" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T48" s="3">
-        <v>1</v>
-      </c>
-      <c r="U48" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="4"/>
-      <c r="AA48" s="4"/>
+      <c r="X48" s="4"/>
+      <c r="Y48" s="4"/>
+      <c r="Z48" s="3"/>
+      <c r="AA48" s="3"/>
       <c r="AB48" s="3"/>
       <c r="AC48" s="3"/>
       <c r="AD48" s="3"/>
@@ -4450,59 +4450,59 @@
     <row r="49" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
       <c r="H49" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I49" s="3"/>
       <c r="J49" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N49" s="3"/>
       <c r="O49" s="3">
         <v>1000</v>
       </c>
       <c r="P49" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q49" s="3">
         <v>30</v>
       </c>
       <c r="R49" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S49" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T49" s="3">
+        <v>1</v>
+      </c>
+      <c r="U49" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S49" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1</v>
-      </c>
-      <c r="U49" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="4"/>
-      <c r="AA49" s="4"/>
+      <c r="X49" s="4"/>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="3"/>
+      <c r="AA49" s="3"/>
       <c r="AB49" s="3"/>
       <c r="AC49" s="3"/>
       <c r="AD49" s="3"/>
@@ -4519,57 +4519,57 @@
     <row r="50" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
       <c r="J50" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N50" s="3"/>
       <c r="O50" s="3">
         <v>300</v>
       </c>
       <c r="P50" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>1</v>
+      </c>
+      <c r="R50" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S50" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q50" s="3">
-        <v>1</v>
-      </c>
-      <c r="R50" s="3" t="s">
+      <c r="T50" s="3">
+        <v>1</v>
+      </c>
+      <c r="U50" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S50" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T50" s="3">
-        <v>1</v>
-      </c>
-      <c r="U50" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="4"/>
-      <c r="AA50" s="4"/>
+      <c r="X50" s="4"/>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="3"/>
+      <c r="AA50" s="3"/>
       <c r="AB50" s="3"/>
       <c r="AC50" s="3"/>
       <c r="AD50" s="3"/>
@@ -4586,57 +4586,57 @@
     <row r="51" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
       <c r="J51" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N51" s="3"/>
       <c r="O51" s="3">
         <v>50</v>
       </c>
       <c r="P51" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>1</v>
+      </c>
+      <c r="R51" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S51" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q51" s="3">
-        <v>1</v>
-      </c>
-      <c r="R51" s="3" t="s">
+      <c r="T51" s="3">
+        <v>1</v>
+      </c>
+      <c r="U51" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S51" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T51" s="3">
-        <v>1</v>
-      </c>
-      <c r="U51" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="4"/>
-      <c r="AA51" s="4"/>
+      <c r="X51" s="4"/>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="3"/>
+      <c r="AA51" s="3"/>
       <c r="AB51" s="3"/>
       <c r="AC51" s="3"/>
       <c r="AD51" s="3"/>
@@ -4653,57 +4653,57 @@
     <row r="52" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
       <c r="J52" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N52" s="3"/>
       <c r="O52" s="3">
         <v>100</v>
       </c>
       <c r="P52" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q52" s="3">
         <v>30</v>
       </c>
       <c r="R52" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S52" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T52" s="3">
+        <v>1</v>
+      </c>
+      <c r="U52" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S52" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T52" s="3">
-        <v>1</v>
-      </c>
-      <c r="U52" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
-      <c r="Y52" s="3"/>
-      <c r="Z52" s="4"/>
-      <c r="AA52" s="4"/>
+      <c r="X52" s="4"/>
+      <c r="Y52" s="4"/>
+      <c r="Z52" s="3"/>
+      <c r="AA52" s="3"/>
       <c r="AB52" s="3"/>
       <c r="AC52" s="3"/>
       <c r="AD52" s="3"/>
@@ -4720,57 +4720,57 @@
     <row r="53" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
       <c r="J53" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N53" s="3"/>
       <c r="O53" s="3">
         <v>10000</v>
       </c>
       <c r="P53" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>1</v>
+      </c>
+      <c r="R53" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S53" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q53" s="3">
-        <v>1</v>
-      </c>
-      <c r="R53" s="3" t="s">
+      <c r="T53" s="3">
+        <v>1</v>
+      </c>
+      <c r="U53" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S53" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T53" s="3">
-        <v>1</v>
-      </c>
-      <c r="U53" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
-      <c r="X53" s="3"/>
-      <c r="Y53" s="3"/>
-      <c r="Z53" s="4"/>
-      <c r="AA53" s="4"/>
+      <c r="X53" s="4"/>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="3"/>
+      <c r="AA53" s="3"/>
       <c r="AB53" s="3"/>
       <c r="AC53" s="3"/>
       <c r="AD53" s="3"/>
@@ -4787,59 +4787,59 @@
     <row r="54" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="E54" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
       <c r="J54" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N54" s="3"/>
       <c r="O54" s="3">
         <v>250000</v>
       </c>
       <c r="P54" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="Q54" s="3">
+        <v>1</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S54" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="Q54" s="3">
-        <v>1</v>
-      </c>
-      <c r="R54" s="3" t="s">
+      <c r="T54" s="3">
+        <v>1</v>
+      </c>
+      <c r="U54" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="T54" s="3">
-        <v>1</v>
-      </c>
-      <c r="U54" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
-      <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
-      <c r="Z54" s="4"/>
-      <c r="AA54" s="4"/>
+      <c r="X54" s="4"/>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="3"/>
+      <c r="AA54" s="3"/>
       <c r="AB54" s="3"/>
       <c r="AC54" s="3"/>
       <c r="AD54" s="3"/>
@@ -4856,59 +4856,59 @@
     <row r="55" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F55" s="3"/>
       <c r="G55" s="3"/>
       <c r="H55" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I55" s="3"/>
       <c r="J55" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N55" s="3"/>
       <c r="O55" s="3">
         <v>2</v>
       </c>
       <c r="P55" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q55" s="3">
         <v>30</v>
       </c>
       <c r="R55" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S55" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T55" s="3">
+        <v>1</v>
+      </c>
+      <c r="U55" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S55" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T55" s="3">
-        <v>1</v>
-      </c>
-      <c r="U55" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
-      <c r="Y55" s="3"/>
-      <c r="Z55" s="4"/>
-      <c r="AA55" s="4"/>
+      <c r="X55" s="4"/>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="3"/>
+      <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
@@ -4925,61 +4925,61 @@
     <row r="56" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
       <c r="J56" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K56" s="3"/>
       <c r="L56" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N56" s="3">
         <v>6.5</v>
       </c>
       <c r="O56" s="3"/>
       <c r="P56" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q56" s="3">
         <v>30</v>
       </c>
       <c r="R56" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S56" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T56" s="3">
         <v>1</v>
       </c>
       <c r="U56" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-      <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
-      <c r="Z56" s="4"/>
-      <c r="AA56" s="4"/>
+      <c r="X56" s="4"/>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="3"/>
+      <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
@@ -4996,61 +4996,61 @@
     <row r="57" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
       <c r="J57" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N57" s="3">
         <v>5.5</v>
       </c>
       <c r="O57" s="3"/>
       <c r="P57" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q57" s="3">
         <v>30</v>
       </c>
       <c r="R57" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S57" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T57" s="3">
         <v>1</v>
       </c>
       <c r="U57" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
-      <c r="X57" s="3"/>
-      <c r="Y57" s="3"/>
-      <c r="Z57" s="4"/>
-      <c r="AA57" s="4"/>
+      <c r="X57" s="4"/>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="3"/>
+      <c r="AA57" s="3"/>
       <c r="AB57" s="3"/>
       <c r="AC57" s="3"/>
       <c r="AD57" s="3"/>
@@ -5067,61 +5067,61 @@
     <row r="58" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
       <c r="J58" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K58" s="3"/>
       <c r="L58" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N58" s="3">
         <v>9.5</v>
       </c>
       <c r="O58" s="3"/>
       <c r="P58" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q58" s="3">
         <v>7</v>
       </c>
       <c r="R58" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S58" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T58" s="3">
         <v>1</v>
       </c>
       <c r="U58" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
-      <c r="X58" s="3"/>
-      <c r="Y58" s="3"/>
-      <c r="Z58" s="4"/>
-      <c r="AA58" s="4"/>
+      <c r="X58" s="4"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="3"/>
+      <c r="AA58" s="3"/>
       <c r="AB58" s="3"/>
       <c r="AC58" s="3"/>
       <c r="AD58" s="3"/>
@@ -5138,61 +5138,61 @@
     <row r="59" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G59" s="3"/>
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
       <c r="J59" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K59" s="3"/>
       <c r="L59" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N59" s="3">
         <v>6</v>
       </c>
       <c r="O59" s="3"/>
       <c r="P59" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q59" s="3">
         <v>7</v>
       </c>
       <c r="R59" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S59" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T59" s="3">
         <v>1</v>
       </c>
       <c r="U59" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
-      <c r="X59" s="3"/>
-      <c r="Y59" s="3"/>
-      <c r="Z59" s="4"/>
-      <c r="AA59" s="4"/>
+      <c r="X59" s="4"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="3"/>
+      <c r="AA59" s="3"/>
       <c r="AB59" s="3"/>
       <c r="AC59" s="3"/>
       <c r="AD59" s="3"/>
@@ -5209,61 +5209,61 @@
     <row r="60" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
       <c r="J60" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K60" s="3"/>
       <c r="L60" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N60" s="3">
         <v>5</v>
       </c>
       <c r="O60" s="3"/>
       <c r="P60" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q60" s="3">
         <v>7</v>
       </c>
       <c r="R60" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S60" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="T60" s="3">
         <v>1</v>
       </c>
       <c r="U60" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V60" s="3"/>
       <c r="W60" s="3"/>
-      <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
-      <c r="Z60" s="4"/>
-      <c r="AA60" s="4"/>
+      <c r="X60" s="4"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="3"/>
+      <c r="AA60" s="3"/>
       <c r="AB60" s="3"/>
       <c r="AC60" s="3"/>
       <c r="AD60" s="3"/>
@@ -5280,61 +5280,61 @@
     <row r="61" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
       <c r="J61" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K61" s="3"/>
       <c r="L61" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N61" s="3">
         <v>4</v>
       </c>
       <c r="O61" s="3"/>
       <c r="P61" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q61" s="3">
         <v>7</v>
       </c>
       <c r="R61" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S61" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="T61" s="3">
         <v>1</v>
       </c>
       <c r="U61" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V61" s="3"/>
       <c r="W61" s="3"/>
-      <c r="X61" s="3"/>
-      <c r="Y61" s="3"/>
-      <c r="Z61" s="4"/>
-      <c r="AA61" s="4"/>
+      <c r="X61" s="4"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="3"/>
+      <c r="AA61" s="3"/>
       <c r="AB61" s="3"/>
       <c r="AC61" s="3"/>
       <c r="AD61" s="3"/>
@@ -5351,61 +5351,61 @@
     <row r="62" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K62" s="3"/>
       <c r="L62" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N62" s="3">
         <v>8</v>
       </c>
       <c r="O62" s="3"/>
       <c r="P62" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q62" s="3">
         <v>1</v>
       </c>
       <c r="R62" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S62" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="T62" s="3">
         <v>1</v>
       </c>
       <c r="U62" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V62" s="3"/>
       <c r="W62" s="3"/>
-      <c r="X62" s="3"/>
-      <c r="Y62" s="3"/>
-      <c r="Z62" s="4"/>
-      <c r="AA62" s="4"/>
+      <c r="X62" s="4"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="3"/>
+      <c r="AA62" s="3"/>
       <c r="AB62" s="3"/>
       <c r="AC62" s="3"/>
       <c r="AD62" s="3"/>
@@ -5422,61 +5422,61 @@
     <row r="63" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
       <c r="J63" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K63" s="3"/>
       <c r="L63" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N63" s="3">
         <v>5</v>
       </c>
       <c r="O63" s="3"/>
       <c r="P63" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q63" s="3">
         <v>1</v>
       </c>
       <c r="R63" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S63" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="T63" s="3">
         <v>1</v>
       </c>
       <c r="U63" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V63" s="3"/>
       <c r="W63" s="3"/>
-      <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="4"/>
-      <c r="AA63" s="4"/>
+      <c r="X63" s="4"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="3"/>
+      <c r="AA63" s="3"/>
       <c r="AB63" s="3"/>
       <c r="AC63" s="3"/>
       <c r="AD63" s="3"/>
@@ -5493,61 +5493,61 @@
     <row r="64" spans="1:39" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
       <c r="J64" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K64" s="3"/>
       <c r="L64" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M64" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N64" s="3">
         <v>4</v>
       </c>
       <c r="O64" s="3"/>
       <c r="P64" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q64" s="3">
         <v>1</v>
       </c>
       <c r="R64" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S64" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="T64" s="3">
         <v>1</v>
       </c>
       <c r="U64" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V64" s="3"/>
       <c r="W64" s="3"/>
-      <c r="X64" s="3"/>
-      <c r="Y64" s="3"/>
-      <c r="Z64" s="4"/>
-      <c r="AA64" s="4"/>
+      <c r="X64" s="4"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="3"/>
+      <c r="AA64" s="3"/>
       <c r="AB64" s="3"/>
       <c r="AC64" s="3"/>
       <c r="AD64" s="3"/>
@@ -5564,61 +5564,61 @@
     <row r="65" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
       <c r="B65" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
       <c r="J65" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K65" s="3"/>
       <c r="L65" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="N65" s="3">
         <v>3</v>
       </c>
       <c r="O65" s="3"/>
       <c r="P65" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="Q65" s="3">
         <v>1</v>
       </c>
       <c r="R65" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="S65" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="T65" s="3">
         <v>1</v>
       </c>
       <c r="U65" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
-      <c r="X65" s="3"/>
-      <c r="Y65" s="3"/>
-      <c r="Z65" s="4"/>
-      <c r="AA65" s="4"/>
+      <c r="X65" s="4"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="3"/>
+      <c r="AA65" s="3"/>
       <c r="AB65" s="3"/>
       <c r="AC65" s="3"/>
       <c r="AD65" s="3"/>
@@ -5635,67 +5635,67 @@
     <row r="66" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
       <c r="B66" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F66" s="3"/>
       <c r="G66" s="3"/>
       <c r="H66" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I66" s="3"/>
       <c r="J66" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K66" s="3"/>
       <c r="L66" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N66" s="3"/>
       <c r="O66" s="3"/>
       <c r="P66" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q66" s="3">
         <v>1</v>
       </c>
       <c r="R66" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="S66" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T66" s="3">
         <v>1</v>
       </c>
       <c r="U66" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="V66" s="3"/>
       <c r="W66" s="3"/>
-      <c r="X66" s="3"/>
-      <c r="Y66" s="3"/>
-      <c r="Z66" s="4"/>
-      <c r="AA66" s="4"/>
+      <c r="X66" s="4"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="3"/>
+      <c r="AA66" s="3"/>
       <c r="AB66" s="3"/>
       <c r="AC66" s="3"/>
       <c r="AD66" s="3"/>
       <c r="AE66" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AF66" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG66" s="3"/>
       <c r="AH66" s="3"/>
@@ -5720,67 +5720,67 @@
     <row r="67" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F67" s="3"/>
       <c r="G67" s="3"/>
       <c r="H67" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="I67" s="3"/>
       <c r="J67" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K67" s="3"/>
       <c r="L67" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q67" s="3">
         <v>1</v>
       </c>
       <c r="R67" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="S67" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="T67" s="3">
         <v>1</v>
       </c>
       <c r="U67" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-      <c r="X67" s="3"/>
-      <c r="Y67" s="3"/>
-      <c r="Z67" s="4"/>
-      <c r="AA67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="3"/>
+      <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="AF67" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="AF67" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
@@ -5805,67 +5805,67 @@
     <row r="68" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F68" s="3"/>
       <c r="G68" s="3"/>
       <c r="H68" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I68" s="3"/>
       <c r="J68" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K68" s="3"/>
       <c r="L68" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N68" s="3"/>
       <c r="O68" s="3"/>
       <c r="P68" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q68" s="3">
         <v>30</v>
       </c>
       <c r="R68" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S68" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T68" s="3">
+        <v>1</v>
+      </c>
+      <c r="U68" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S68" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T68" s="3">
-        <v>1</v>
-      </c>
-      <c r="U68" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V68" s="3"/>
       <c r="W68" s="3"/>
-      <c r="X68" s="3"/>
-      <c r="Y68" s="3"/>
-      <c r="Z68" s="4"/>
-      <c r="AA68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="3"/>
+      <c r="AA68" s="3"/>
       <c r="AB68" s="3"/>
       <c r="AC68" s="3"/>
       <c r="AD68" s="3"/>
       <c r="AE68" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AF68" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AG68" s="3"/>
       <c r="AH68" s="3"/>
@@ -5874,7 +5874,7 @@
       <c r="AK68" s="3"/>
       <c r="AL68" s="3"/>
       <c r="AM68" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AN68" s="5">
         <v>5.7700000000000001E-2</v>
@@ -5907,67 +5907,67 @@
     <row r="69" spans="1:48" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F69" s="3"/>
       <c r="G69" s="3"/>
       <c r="H69" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="I69" s="3"/>
       <c r="J69" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="K69" s="3"/>
       <c r="L69" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N69" s="3"/>
       <c r="O69" s="3"/>
       <c r="P69" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="Q69" s="3">
         <v>30</v>
       </c>
       <c r="R69" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="S69" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="T69" s="3">
+        <v>1</v>
+      </c>
+      <c r="U69" s="3" t="s">
         <v>45</v>
-      </c>
-      <c r="S69" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="T69" s="3">
-        <v>1</v>
-      </c>
-      <c r="U69" s="3" t="s">
-        <v>47</v>
       </c>
       <c r="V69" s="3"/>
       <c r="W69" s="3"/>
-      <c r="X69" s="3"/>
-      <c r="Y69" s="3"/>
-      <c r="Z69" s="4"/>
-      <c r="AA69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="3"/>
+      <c r="AA69" s="3"/>
       <c r="AB69" s="3"/>
       <c r="AC69" s="3"/>
       <c r="AD69" s="3"/>
       <c r="AE69" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AF69" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AG69" s="3"/>
       <c r="AH69" s="3"/>
@@ -5976,7 +5976,7 @@
       <c r="AK69" s="3"/>
       <c r="AL69" s="3"/>
       <c r="AM69" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AN69" s="5">
         <v>5.7700000000000001E-2</v>
